--- a/dev_docs/千界万锻数值表格-26_4_21.xlsx
+++ b/dev_docs/千界万锻数值表格-26_4_21.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\AppData\Roaming\PrismLauncher\instances\SenDimsBanForges\minecraft\dev_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B723991-BF70-435F-83B5-B9D8F8562ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC49CA77-7BB2-470C-94C9-EE0CD95FB092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6195" yWindow="4275" windowWidth="26430" windowHeight="15435" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-6720" windowWidth="30936" windowHeight="18816" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="数值分配" sheetId="3" r:id="rId1"/>
@@ -1316,7 +1316,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1503,22 +1503,28 @@
     <xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="7" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="7" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1982,57 +1988,57 @@
     </row>
     <row r="3" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C3" s="21"/>
-      <c r="D3" s="68" t="s">
+      <c r="D3" s="70" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="68"/>
-      <c r="O3" s="68"/>
-      <c r="P3" s="68"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="70"/>
+      <c r="I3" s="70"/>
+      <c r="J3" s="70"/>
+      <c r="K3" s="70"/>
+      <c r="L3" s="70"/>
+      <c r="M3" s="70"/>
+      <c r="N3" s="70"/>
+      <c r="O3" s="70"/>
+      <c r="P3" s="70"/>
       <c r="Q3" s="21"/>
       <c r="R3" s="21"/>
       <c r="S3" s="21"/>
       <c r="T3" s="21"/>
-      <c r="V3" s="68" t="s">
+      <c r="V3" s="70" t="s">
         <v>52</v>
       </c>
-      <c r="W3" s="68"/>
-      <c r="X3" s="68"/>
-      <c r="Y3" s="68"/>
-      <c r="Z3" s="68"/>
-      <c r="AA3" s="68"/>
-      <c r="AB3" s="68"/>
-      <c r="AC3" s="68"/>
-      <c r="AD3" s="68"/>
-      <c r="AE3" s="68"/>
-      <c r="AF3" s="68"/>
-      <c r="AG3" s="68"/>
-      <c r="AH3" s="68"/>
-      <c r="AI3" s="68"/>
-      <c r="AJ3" s="68"/>
-      <c r="AK3" s="68"/>
-      <c r="AL3" s="68"/>
-      <c r="AM3" s="68"/>
-      <c r="AN3" s="68"/>
-      <c r="AO3" s="68"/>
-      <c r="AP3" s="68"/>
-      <c r="AQ3" s="68"/>
-      <c r="AR3" s="68"/>
-      <c r="AS3" s="68"/>
-      <c r="AT3" s="68"/>
-      <c r="AU3" s="68"/>
-      <c r="AV3" s="68"/>
-      <c r="AW3" s="68"/>
-      <c r="AX3" s="68"/>
-      <c r="AY3" s="68"/>
+      <c r="W3" s="70"/>
+      <c r="X3" s="70"/>
+      <c r="Y3" s="70"/>
+      <c r="Z3" s="70"/>
+      <c r="AA3" s="70"/>
+      <c r="AB3" s="70"/>
+      <c r="AC3" s="70"/>
+      <c r="AD3" s="70"/>
+      <c r="AE3" s="70"/>
+      <c r="AF3" s="70"/>
+      <c r="AG3" s="70"/>
+      <c r="AH3" s="70"/>
+      <c r="AI3" s="70"/>
+      <c r="AJ3" s="70"/>
+      <c r="AK3" s="70"/>
+      <c r="AL3" s="70"/>
+      <c r="AM3" s="70"/>
+      <c r="AN3" s="70"/>
+      <c r="AO3" s="70"/>
+      <c r="AP3" s="70"/>
+      <c r="AQ3" s="70"/>
+      <c r="AR3" s="70"/>
+      <c r="AS3" s="70"/>
+      <c r="AT3" s="70"/>
+      <c r="AU3" s="70"/>
+      <c r="AV3" s="70"/>
+      <c r="AW3" s="70"/>
+      <c r="AX3" s="70"/>
+      <c r="AY3" s="70"/>
       <c r="AZ3" s="21"/>
     </row>
     <row r="4" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
@@ -2078,44 +2084,44 @@
       <c r="R4" s="21"/>
       <c r="S4" s="21"/>
       <c r="T4" s="21"/>
-      <c r="V4" s="69" t="s">
+      <c r="V4" s="71" t="s">
         <v>57</v>
       </c>
-      <c r="W4" s="69"/>
-      <c r="X4" s="69"/>
-      <c r="Y4" s="69"/>
-      <c r="Z4" s="69"/>
-      <c r="AA4" s="69"/>
+      <c r="W4" s="71"/>
+      <c r="X4" s="71"/>
+      <c r="Y4" s="71"/>
+      <c r="Z4" s="71"/>
+      <c r="AA4" s="71"/>
       <c r="AB4" s="21"/>
       <c r="AC4" s="21"/>
-      <c r="AD4" s="69" t="s">
+      <c r="AD4" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="AE4" s="69"/>
-      <c r="AF4" s="69"/>
-      <c r="AG4" s="69"/>
+      <c r="AE4" s="71"/>
+      <c r="AF4" s="71"/>
+      <c r="AG4" s="71"/>
       <c r="AH4" s="21"/>
       <c r="AI4" s="21"/>
       <c r="AJ4" s="21"/>
       <c r="AK4" s="21"/>
-      <c r="AL4" s="69" t="s">
+      <c r="AL4" s="71" t="s">
         <v>60</v>
       </c>
-      <c r="AM4" s="69"/>
-      <c r="AN4" s="69"/>
-      <c r="AO4" s="69"/>
-      <c r="AP4" s="69"/>
-      <c r="AQ4" s="69"/>
+      <c r="AM4" s="71"/>
+      <c r="AN4" s="71"/>
+      <c r="AO4" s="71"/>
+      <c r="AP4" s="71"/>
+      <c r="AQ4" s="71"/>
       <c r="AR4" s="21"/>
       <c r="AS4" s="21"/>
-      <c r="AT4" s="69" t="s">
+      <c r="AT4" s="71" t="s">
         <v>61</v>
       </c>
-      <c r="AU4" s="69"/>
-      <c r="AV4" s="69"/>
-      <c r="AW4" s="69"/>
-      <c r="AX4" s="69"/>
-      <c r="AY4" s="69"/>
+      <c r="AU4" s="71"/>
+      <c r="AV4" s="71"/>
+      <c r="AW4" s="71"/>
+      <c r="AX4" s="71"/>
+      <c r="AY4" s="71"/>
       <c r="AZ4" s="21"/>
     </row>
     <row r="5" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
@@ -2257,7 +2263,7 @@
       </c>
     </row>
     <row r="6" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B6" s="70">
+      <c r="B6" s="72">
         <v>0</v>
       </c>
       <c r="C6" s="19">
@@ -2421,7 +2427,7 @@
       </c>
     </row>
     <row r="7" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B7" s="70"/>
+      <c r="B7" s="72"/>
       <c r="C7" s="19">
         <v>1.1000000000000001</v>
       </c>
@@ -2583,7 +2589,7 @@
       </c>
     </row>
     <row r="8" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B8" s="70">
+      <c r="B8" s="72">
         <v>1</v>
       </c>
       <c r="C8" s="18">
@@ -2747,7 +2753,7 @@
       </c>
     </row>
     <row r="9" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="70"/>
+      <c r="B9" s="72"/>
       <c r="C9" s="19">
         <v>1.3</v>
       </c>
@@ -2909,7 +2915,7 @@
       </c>
     </row>
     <row r="10" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B10" s="71">
+      <c r="B10" s="73">
         <v>2</v>
       </c>
       <c r="C10" s="18">
@@ -3073,10 +3079,10 @@
       </c>
     </row>
     <row r="11" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B11" s="71"/>
+      <c r="B11" s="73"/>
     </row>
     <row r="12" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="71"/>
+      <c r="B12" s="73"/>
       <c r="C12" s="19">
         <v>2.1</v>
       </c>
@@ -3238,7 +3244,7 @@
       </c>
     </row>
     <row r="13" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B13" s="70">
+      <c r="B13" s="72">
         <v>3</v>
       </c>
       <c r="C13" s="18">
@@ -3402,7 +3408,7 @@
       </c>
     </row>
     <row r="14" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B14" s="70"/>
+      <c r="B14" s="72"/>
       <c r="C14" s="19">
         <v>2.2999999999999998</v>
       </c>
@@ -3564,7 +3570,7 @@
       </c>
     </row>
     <row r="16" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="70">
+      <c r="B16" s="72">
         <v>4</v>
       </c>
       <c r="C16" s="19">
@@ -3728,7 +3734,7 @@
       </c>
     </row>
     <row r="17" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="70"/>
+      <c r="B17" s="72"/>
       <c r="C17" s="18">
         <v>3.2</v>
       </c>
@@ -3890,7 +3896,7 @@
       </c>
     </row>
     <row r="18" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="70"/>
+      <c r="B18" s="72"/>
       <c r="C18" s="19">
         <v>3.3</v>
       </c>
@@ -4052,7 +4058,7 @@
       </c>
     </row>
     <row r="20" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="70">
+      <c r="B20" s="72">
         <v>5</v>
       </c>
       <c r="C20" s="18">
@@ -4216,7 +4222,7 @@
       </c>
     </row>
     <row r="21" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="70"/>
+      <c r="B21" s="72"/>
       <c r="C21" s="19">
         <v>4.2</v>
       </c>
@@ -4417,30 +4423,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E1" s="82" t="s">
+      <c r="E1" s="84" t="s">
         <v>96</v>
       </c>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
-      <c r="H1" s="82"/>
+      <c r="F1" s="84"/>
+      <c r="G1" s="84"/>
+      <c r="H1" s="84"/>
       <c r="I1" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="K1" s="83" t="s">
+      <c r="K1" s="85" t="s">
         <v>97</v>
       </c>
-      <c r="L1" s="83"/>
-      <c r="M1" s="83"/>
-      <c r="N1" s="83"/>
+      <c r="L1" s="85"/>
+      <c r="M1" s="85"/>
+      <c r="N1" s="85"/>
       <c r="O1" s="38" t="s">
         <v>159</v>
       </c>
-      <c r="Q1" s="84" t="s">
+      <c r="Q1" s="86" t="s">
         <v>98</v>
       </c>
-      <c r="R1" s="84"/>
-      <c r="S1" s="84"/>
-      <c r="T1" s="84"/>
+      <c r="R1" s="86"/>
+      <c r="S1" s="86"/>
+      <c r="T1" s="86"/>
       <c r="U1" s="39" t="s">
         <v>159</v>
       </c>
@@ -4449,35 +4455,35 @@
       <c r="A2" s="40" t="s">
         <v>158</v>
       </c>
-      <c r="B2" s="85" t="s">
+      <c r="B2" s="87" t="s">
         <v>157</v>
       </c>
-      <c r="C2" s="85"/>
-      <c r="D2" s="85"/>
-      <c r="E2" s="100" t="s">
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="102" t="s">
         <v>196</v>
       </c>
-      <c r="F2" s="100"/>
-      <c r="G2" s="100" t="s">
+      <c r="F2" s="102"/>
+      <c r="G2" s="102" t="s">
         <v>197</v>
       </c>
-      <c r="H2" s="100"/>
-      <c r="K2" s="100" t="s">
+      <c r="H2" s="102"/>
+      <c r="K2" s="102" t="s">
         <v>196</v>
       </c>
-      <c r="L2" s="100"/>
-      <c r="M2" s="100" t="s">
+      <c r="L2" s="102"/>
+      <c r="M2" s="102" t="s">
         <v>197</v>
       </c>
-      <c r="N2" s="100"/>
-      <c r="Q2" s="100" t="s">
+      <c r="N2" s="102"/>
+      <c r="Q2" s="102" t="s">
         <v>196</v>
       </c>
-      <c r="R2" s="100"/>
-      <c r="S2" s="100" t="s">
+      <c r="R2" s="102"/>
+      <c r="S2" s="102" t="s">
         <v>197</v>
       </c>
-      <c r="T2" s="100"/>
+      <c r="T2" s="102"/>
     </row>
     <row r="3" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="41">
@@ -4490,25 +4496,25 @@
         <v>122</v>
       </c>
       <c r="D3" s="1"/>
-      <c r="E3" s="86"/>
-      <c r="F3" s="87"/>
-      <c r="G3" s="87"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="98" t="s">
+      <c r="E3" s="88"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="90"/>
+      <c r="I3" s="100" t="s">
         <v>129</v>
       </c>
-      <c r="K3" s="86"/>
-      <c r="L3" s="87"/>
-      <c r="M3" s="87"/>
-      <c r="N3" s="88"/>
+      <c r="K3" s="88"/>
+      <c r="L3" s="89"/>
+      <c r="M3" s="89"/>
+      <c r="N3" s="90"/>
       <c r="O3" s="45" t="s">
         <v>129</v>
       </c>
-      <c r="Q3" s="86"/>
-      <c r="R3" s="87"/>
-      <c r="S3" s="87"/>
-      <c r="T3" s="88"/>
-      <c r="U3" s="80" t="s">
+      <c r="Q3" s="88"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="90"/>
+      <c r="U3" s="82" t="s">
         <v>156</v>
       </c>
     </row>
@@ -4521,11 +4527,11 @@
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="89"/>
-      <c r="F4" s="90"/>
-      <c r="G4" s="90"/>
-      <c r="H4" s="91"/>
-      <c r="I4" s="99"/>
+      <c r="E4" s="91"/>
+      <c r="F4" s="92"/>
+      <c r="G4" s="92"/>
+      <c r="H4" s="93"/>
+      <c r="I4" s="101"/>
       <c r="K4" s="49" t="s">
         <v>133</v>
       </c>
@@ -4534,14 +4540,14 @@
         <v>134</v>
       </c>
       <c r="N4" s="47"/>
-      <c r="O4" s="95">
+      <c r="O4" s="97">
         <v>0</v>
       </c>
-      <c r="Q4" s="92"/>
-      <c r="R4" s="93"/>
-      <c r="S4" s="93"/>
-      <c r="T4" s="94"/>
-      <c r="U4" s="81"/>
+      <c r="Q4" s="94"/>
+      <c r="R4" s="95"/>
+      <c r="S4" s="95"/>
+      <c r="T4" s="96"/>
+      <c r="U4" s="83"/>
     </row>
     <row r="5" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="42">
@@ -4568,7 +4574,7 @@
       <c r="H5" s="48" t="s">
         <v>132</v>
       </c>
-      <c r="I5" s="75">
+      <c r="I5" s="77">
         <v>0</v>
       </c>
       <c r="K5" s="48" t="s">
@@ -4579,12 +4585,12 @@
         <v>194</v>
       </c>
       <c r="N5" s="47"/>
-      <c r="O5" s="96"/>
-      <c r="Q5" s="92"/>
-      <c r="R5" s="93"/>
-      <c r="S5" s="93"/>
-      <c r="T5" s="94"/>
-      <c r="U5" s="81"/>
+      <c r="O5" s="98"/>
+      <c r="Q5" s="94"/>
+      <c r="R5" s="95"/>
+      <c r="S5" s="95"/>
+      <c r="T5" s="96"/>
+      <c r="U5" s="83"/>
     </row>
     <row r="6" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="42">
@@ -4601,19 +4607,19 @@
         <v>160</v>
       </c>
       <c r="H6" s="47"/>
-      <c r="I6" s="75"/>
+      <c r="I6" s="77"/>
       <c r="K6" s="48" t="s">
         <v>165</v>
       </c>
       <c r="L6" s="48"/>
       <c r="M6" s="48"/>
       <c r="N6" s="47"/>
-      <c r="O6" s="96"/>
-      <c r="Q6" s="89"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90"/>
-      <c r="T6" s="91"/>
-      <c r="U6" s="81"/>
+      <c r="O6" s="98"/>
+      <c r="Q6" s="91"/>
+      <c r="R6" s="92"/>
+      <c r="S6" s="92"/>
+      <c r="T6" s="93"/>
+      <c r="U6" s="83"/>
     </row>
     <row r="7" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="42">
@@ -4634,7 +4640,7 @@
         <v>164</v>
       </c>
       <c r="H7" s="47"/>
-      <c r="I7" s="75"/>
+      <c r="I7" s="77"/>
       <c r="K7" s="48" t="s">
         <v>167</v>
       </c>
@@ -4643,7 +4649,7 @@
         <v>166</v>
       </c>
       <c r="N7" s="47"/>
-      <c r="O7" s="97"/>
+      <c r="O7" s="99"/>
       <c r="Q7" s="54" t="s">
         <v>199</v>
       </c>
@@ -4656,7 +4662,7 @@
       <c r="T7" s="51" t="s">
         <v>173</v>
       </c>
-      <c r="U7" s="76">
+      <c r="U7" s="78">
         <v>1</v>
       </c>
     </row>
@@ -4681,7 +4687,7 @@
         <v>169</v>
       </c>
       <c r="H8" s="47"/>
-      <c r="I8" s="75"/>
+      <c r="I8" s="77"/>
       <c r="K8" s="53" t="s">
         <v>136</v>
       </c>
@@ -4694,7 +4700,7 @@
       <c r="N8" s="51" t="s">
         <v>170</v>
       </c>
-      <c r="O8" s="76">
+      <c r="O8" s="78">
         <v>1</v>
       </c>
       <c r="Q8" s="51" t="s">
@@ -4707,7 +4713,7 @@
       <c r="T8" s="51" t="s">
         <v>198</v>
       </c>
-      <c r="U8" s="76"/>
+      <c r="U8" s="78"/>
     </row>
     <row r="9" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="43">
@@ -4732,7 +4738,7 @@
       <c r="H9" s="50" t="s">
         <v>139</v>
       </c>
-      <c r="I9" s="76">
+      <c r="I9" s="78">
         <v>1</v>
       </c>
       <c r="K9" s="51" t="s">
@@ -4747,7 +4753,7 @@
       <c r="N9" s="51" t="s">
         <v>179</v>
       </c>
-      <c r="O9" s="76"/>
+      <c r="O9" s="78"/>
       <c r="Q9" s="33" t="s">
         <v>180</v>
       </c>
@@ -4756,7 +4762,7 @@
         <v>181</v>
       </c>
       <c r="T9" s="56"/>
-      <c r="U9" s="77">
+      <c r="U9" s="79">
         <v>2</v>
       </c>
     </row>
@@ -4775,7 +4781,7 @@
       <c r="F10" s="52"/>
       <c r="G10" s="52"/>
       <c r="H10" s="52"/>
-      <c r="I10" s="76"/>
+      <c r="I10" s="78"/>
       <c r="K10" s="57" t="s">
         <v>141</v>
       </c>
@@ -4786,7 +4792,7 @@
       <c r="N10" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="O10" s="77">
+      <c r="O10" s="79">
         <v>2</v>
       </c>
       <c r="Q10" s="33" t="s">
@@ -4795,10 +4801,10 @@
       <c r="R10" s="56"/>
       <c r="S10" s="56"/>
       <c r="T10" s="56"/>
-      <c r="U10" s="77"/>
+      <c r="U10" s="79"/>
     </row>
     <row r="11" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="67">
+      <c r="A11" s="65">
         <v>3.1</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -4818,7 +4824,7 @@
       <c r="H11" s="55" t="s">
         <v>145</v>
       </c>
-      <c r="I11" s="77">
+      <c r="I11" s="79">
         <v>2</v>
       </c>
       <c r="K11" s="33"/>
@@ -4827,7 +4833,7 @@
         <v>184</v>
       </c>
       <c r="N11" s="56"/>
-      <c r="O11" s="77"/>
+      <c r="O11" s="79"/>
       <c r="Q11" s="61" t="s">
         <v>183</v>
       </c>
@@ -4836,12 +4842,12 @@
         <v>185</v>
       </c>
       <c r="T11" s="59"/>
-      <c r="U11" s="78">
+      <c r="U11" s="80">
         <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="67">
+      <c r="A12" s="65">
         <v>3.2</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -4857,24 +4863,24 @@
         <v>186</v>
       </c>
       <c r="H12" s="56"/>
-      <c r="I12" s="77"/>
+      <c r="I12" s="79"/>
       <c r="K12" s="33"/>
       <c r="L12" s="56"/>
       <c r="M12" s="33" t="s">
         <v>187</v>
       </c>
       <c r="N12" s="56"/>
-      <c r="O12" s="77"/>
-      <c r="Q12" s="62" t="s">
+      <c r="O12" s="79"/>
+      <c r="Q12" s="69" t="s">
         <v>152</v>
       </c>
       <c r="R12" s="59"/>
       <c r="S12" s="59"/>
       <c r="T12" s="59"/>
-      <c r="U12" s="78"/>
+      <c r="U12" s="80"/>
     </row>
     <row r="13" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="67">
+      <c r="A13" s="65">
         <v>3.3</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -4892,7 +4898,7 @@
       <c r="F13" s="33"/>
       <c r="G13" s="33"/>
       <c r="H13" s="56"/>
-      <c r="I13" s="77"/>
+      <c r="I13" s="79"/>
       <c r="K13" s="60" t="s">
         <v>146</v>
       </c>
@@ -4914,9 +4920,9 @@
       <c r="R13" s="28" t="s">
         <v>192</v>
       </c>
-      <c r="S13" s="64"/>
-      <c r="T13" s="64"/>
-      <c r="U13" s="79">
+      <c r="S13" s="63"/>
+      <c r="T13" s="63"/>
+      <c r="U13" s="81">
         <v>4</v>
       </c>
     </row>
@@ -4931,31 +4937,31 @@
         <v>120</v>
       </c>
       <c r="D14" s="1"/>
-      <c r="E14" s="58" t="s">
+      <c r="E14" s="66" t="s">
         <v>149</v>
       </c>
       <c r="F14" s="58"/>
       <c r="G14" s="61"/>
       <c r="H14" s="59"/>
-      <c r="I14" s="78">
+      <c r="I14" s="80">
         <v>3</v>
       </c>
-      <c r="K14" s="63"/>
-      <c r="L14" s="63"/>
+      <c r="K14" s="62"/>
+      <c r="L14" s="62"/>
       <c r="M14" s="28" t="s">
         <v>148</v>
       </c>
-      <c r="N14" s="64"/>
-      <c r="O14" s="73">
+      <c r="N14" s="63"/>
+      <c r="O14" s="75">
         <v>4</v>
       </c>
-      <c r="Q14" s="28" t="s">
+      <c r="Q14" s="67" t="s">
         <v>152</v>
       </c>
-      <c r="R14" s="64"/>
-      <c r="S14" s="64"/>
-      <c r="T14" s="64"/>
-      <c r="U14" s="79"/>
+      <c r="R14" s="63"/>
+      <c r="S14" s="63"/>
+      <c r="T14" s="63"/>
+      <c r="U14" s="81"/>
     </row>
     <row r="15" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="44">
@@ -4972,29 +4978,29 @@
       <c r="F15" s="59"/>
       <c r="G15" s="59"/>
       <c r="H15" s="59"/>
-      <c r="I15" s="78"/>
-      <c r="K15" s="63"/>
-      <c r="L15" s="64"/>
+      <c r="I15" s="80"/>
+      <c r="K15" s="62"/>
+      <c r="L15" s="63"/>
       <c r="M15" s="28" t="s">
         <v>151</v>
       </c>
-      <c r="N15" s="64"/>
-      <c r="O15" s="74"/>
-      <c r="Q15" s="65" t="s">
+      <c r="N15" s="63"/>
+      <c r="O15" s="76"/>
+      <c r="Q15" s="68" t="s">
         <v>152</v>
       </c>
-      <c r="R15" s="66"/>
-      <c r="S15" s="66"/>
-      <c r="T15" s="66"/>
+      <c r="R15" s="64"/>
+      <c r="S15" s="64"/>
+      <c r="T15" s="64"/>
       <c r="U15" s="44">
         <v>5</v>
       </c>
     </row>
     <row r="18" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C18" s="72" t="s">
+      <c r="C18" s="74" t="s">
         <v>99</v>
       </c>
-      <c r="D18" s="72"/>
+      <c r="D18" s="74"/>
     </row>
     <row r="19" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="3" t="s">
@@ -5108,32 +5114,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A1" s="111" t="s">
+      <c r="A1" s="113" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="111"/>
-      <c r="C1" s="111"/>
-      <c r="D1" s="111"/>
-      <c r="E1" s="111"/>
-      <c r="G1" s="111" t="s">
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="G1" s="113" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="111"/>
-      <c r="I1" s="111"/>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
-      <c r="V1" s="111"/>
-      <c r="W1" s="111"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
+      <c r="V1" s="113"/>
+      <c r="W1" s="113"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
@@ -5199,32 +5205,32 @@
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A8" s="101" t="s">
+      <c r="A8" s="103" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="102"/>
-      <c r="C8" s="102"/>
-      <c r="D8" s="102"/>
-      <c r="E8" s="102"/>
-      <c r="F8" s="103"/>
+      <c r="B8" s="104"/>
+      <c r="C8" s="104"/>
+      <c r="D8" s="104"/>
+      <c r="E8" s="104"/>
+      <c r="F8" s="105"/>
       <c r="G8" s="4"/>
-      <c r="I8" s="101" t="s">
+      <c r="I8" s="103" t="s">
         <v>10</v>
       </c>
-      <c r="J8" s="102"/>
-      <c r="K8" s="102"/>
-      <c r="L8" s="102"/>
-      <c r="M8" s="102"/>
-      <c r="N8" s="103"/>
+      <c r="J8" s="104"/>
+      <c r="K8" s="104"/>
+      <c r="L8" s="104"/>
+      <c r="M8" s="104"/>
+      <c r="N8" s="105"/>
       <c r="O8" s="1"/>
-      <c r="Q8" s="101" t="s">
+      <c r="Q8" s="103" t="s">
         <v>11</v>
       </c>
-      <c r="R8" s="102"/>
-      <c r="S8" s="102"/>
-      <c r="T8" s="102"/>
-      <c r="U8" s="102"/>
-      <c r="V8" s="103"/>
+      <c r="R8" s="104"/>
+      <c r="S8" s="104"/>
+      <c r="T8" s="104"/>
+      <c r="U8" s="104"/>
+      <c r="V8" s="105"/>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
@@ -5306,11 +5312,11 @@
         <f t="shared" ref="E10:E15" si="0">D10*B10</f>
         <v>0.5</v>
       </c>
-      <c r="F10" s="107">
+      <c r="F10" s="109">
         <f>D10+D11+D12+D13</f>
         <v>2</v>
       </c>
-      <c r="G10" s="72">
+      <c r="G10" s="74">
         <v>1.5</v>
       </c>
       <c r="I10" s="1" t="s">
@@ -5330,11 +5336,11 @@
         <f t="shared" ref="M10:M16" si="2">L10*J10</f>
         <v>0.5</v>
       </c>
-      <c r="N10" s="107">
+      <c r="N10" s="109">
         <f>L10+L11+L12+L13+L14+L15+L16</f>
         <v>3.5</v>
       </c>
-      <c r="O10" s="72">
+      <c r="O10" s="74">
         <v>4</v>
       </c>
       <c r="Q10" s="1" t="s">
@@ -5354,7 +5360,7 @@
         <f>T10*R10</f>
         <v>0.5</v>
       </c>
-      <c r="V10" s="104">
+      <c r="V10" s="106">
         <f>T10+T11+T12</f>
         <v>1.84</v>
       </c>
@@ -5377,8 +5383,8 @@
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="F11" s="110"/>
-      <c r="G11" s="72"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="74"/>
       <c r="I11" s="1" t="s">
         <v>19</v>
       </c>
@@ -5396,8 +5402,8 @@
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
-      <c r="N11" s="110"/>
-      <c r="O11" s="72"/>
+      <c r="N11" s="112"/>
+      <c r="O11" s="74"/>
       <c r="Q11" s="1" t="s">
         <v>19</v>
       </c>
@@ -5415,7 +5421,7 @@
         <f>T11*R11</f>
         <v>0.5</v>
       </c>
-      <c r="V11" s="105"/>
+      <c r="V11" s="107"/>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
@@ -5435,8 +5441,8 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F12" s="110"/>
-      <c r="G12" s="72"/>
+      <c r="F12" s="112"/>
+      <c r="G12" s="74"/>
       <c r="I12" s="1" t="s">
         <v>20</v>
       </c>
@@ -5454,8 +5460,8 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="N12" s="110"/>
-      <c r="O12" s="72"/>
+      <c r="N12" s="112"/>
+      <c r="O12" s="74"/>
       <c r="Q12" s="1" t="s">
         <v>21</v>
       </c>
@@ -5473,7 +5479,7 @@
         <f>T12*R12</f>
         <v>1.6800000000000002</v>
       </c>
-      <c r="V12" s="106"/>
+      <c r="V12" s="108"/>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
@@ -5493,8 +5499,8 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F13" s="108"/>
-      <c r="G13" s="72"/>
+      <c r="F13" s="110"/>
+      <c r="G13" s="74"/>
       <c r="I13" s="1" t="s">
         <v>23</v>
       </c>
@@ -5512,8 +5518,8 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="N13" s="110"/>
-      <c r="O13" s="72"/>
+      <c r="N13" s="112"/>
+      <c r="O13" s="74"/>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
@@ -5533,11 +5539,11 @@
         <f t="shared" si="0"/>
         <v>1.575</v>
       </c>
-      <c r="F14" s="107">
+      <c r="F14" s="109">
         <f>D10+D11+D12+D14+D15</f>
         <v>3.09375</v>
       </c>
-      <c r="G14" s="72">
+      <c r="G14" s="74">
         <v>3</v>
       </c>
       <c r="I14" s="1" t="s">
@@ -5557,8 +5563,8 @@
         <f t="shared" si="2"/>
         <v>3.5</v>
       </c>
-      <c r="N14" s="110"/>
-      <c r="O14" s="72"/>
+      <c r="N14" s="112"/>
+      <c r="O14" s="74"/>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
@@ -5578,8 +5584,8 @@
         <f t="shared" si="0"/>
         <v>2.4187500000000002</v>
       </c>
-      <c r="F15" s="108"/>
-      <c r="G15" s="72"/>
+      <c r="F15" s="110"/>
+      <c r="G15" s="74"/>
       <c r="I15" s="1" t="s">
         <v>27</v>
       </c>
@@ -5597,8 +5603,8 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="N15" s="110"/>
-      <c r="O15" s="72"/>
+      <c r="N15" s="112"/>
+      <c r="O15" s="74"/>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.15">
       <c r="D16" s="6" t="s">
@@ -5629,8 +5635,8 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="N16" s="108"/>
-      <c r="O16" s="72"/>
+      <c r="N16" s="110"/>
+      <c r="O16" s="74"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D17" s="6" t="s">
@@ -5679,21 +5685,21 @@
       <c r="F19" s="6"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A20" s="101" t="s">
+      <c r="A20" s="103" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="102"/>
-      <c r="C20" s="102"/>
-      <c r="D20" s="102"/>
-      <c r="E20" s="103"/>
-      <c r="I20" s="101" t="s">
+      <c r="B20" s="104"/>
+      <c r="C20" s="104"/>
+      <c r="D20" s="104"/>
+      <c r="E20" s="105"/>
+      <c r="I20" s="103" t="s">
         <v>30</v>
       </c>
-      <c r="J20" s="102"/>
-      <c r="K20" s="102"/>
-      <c r="L20" s="102"/>
-      <c r="M20" s="102"/>
-      <c r="N20" s="103"/>
+      <c r="J20" s="104"/>
+      <c r="K20" s="104"/>
+      <c r="L20" s="104"/>
+      <c r="M20" s="104"/>
+      <c r="N20" s="105"/>
       <c r="O20" s="5"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.15">
@@ -5766,7 +5772,7 @@
         <f t="shared" ref="M22:M26" si="3">L22*J22</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N22" s="104">
+      <c r="N22" s="106">
         <f>L22+L23+L24</f>
         <v>0.84000000000000008</v>
       </c>
@@ -5806,7 +5812,7 @@
         <f t="shared" si="3"/>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N23" s="105"/>
+      <c r="N23" s="107"/>
       <c r="O23" s="5"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.15">
@@ -5843,7 +5849,7 @@
         <f t="shared" si="3"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="N24" s="106"/>
+      <c r="N24" s="108"/>
       <c r="O24" s="5"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.15">
@@ -5880,7 +5886,7 @@
         <f t="shared" si="3"/>
         <v>0.68</v>
       </c>
-      <c r="N25" s="104">
+      <c r="N25" s="106">
         <f>L22+L23+L25+L26</f>
         <v>1.2400000000000002</v>
       </c>
@@ -5903,7 +5909,7 @@
         <f t="shared" si="3"/>
         <v>0.68</v>
       </c>
-      <c r="N26" s="106"/>
+      <c r="N26" s="108"/>
       <c r="O26" s="5"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.15">
@@ -5917,23 +5923,23 @@
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A30" s="109" t="s">
+      <c r="A30" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="B30" s="102"/>
-      <c r="C30" s="102"/>
-      <c r="D30" s="102"/>
-      <c r="E30" s="102"/>
-      <c r="F30" s="103"/>
+      <c r="B30" s="104"/>
+      <c r="C30" s="104"/>
+      <c r="D30" s="104"/>
+      <c r="E30" s="104"/>
+      <c r="F30" s="105"/>
       <c r="G30" s="4"/>
-      <c r="I30" s="109" t="s">
+      <c r="I30" s="111" t="s">
         <v>44</v>
       </c>
-      <c r="J30" s="102"/>
-      <c r="K30" s="102"/>
-      <c r="L30" s="102"/>
-      <c r="M30" s="102"/>
-      <c r="N30" s="103"/>
+      <c r="J30" s="104"/>
+      <c r="K30" s="104"/>
+      <c r="L30" s="104"/>
+      <c r="M30" s="104"/>
+      <c r="N30" s="105"/>
       <c r="O30" s="1"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.15">
@@ -5998,11 +6004,11 @@
         <f t="shared" ref="E32:E37" si="4">D32*B32</f>
         <v>0.70724999999999993</v>
       </c>
-      <c r="F32" s="107">
+      <c r="F32" s="109">
         <f>D32+D33+D34+D35</f>
         <v>2.8634999999999997</v>
       </c>
-      <c r="G32" s="72">
+      <c r="G32" s="74">
         <v>1.5</v>
       </c>
       <c r="I32" s="1" t="s">
@@ -6022,11 +6028,11 @@
         <f t="shared" ref="M32:M38" si="6">L32*J32</f>
         <v>0.70724999999999993</v>
       </c>
-      <c r="N32" s="107">
+      <c r="N32" s="109">
         <f>L32+L33+L34+L35+L36+L37+L38</f>
         <v>4.4731499999999995</v>
       </c>
-      <c r="O32" s="72">
+      <c r="O32" s="74">
         <v>4</v>
       </c>
     </row>
@@ -6048,8 +6054,8 @@
         <f t="shared" si="4"/>
         <v>0.70724999999999993</v>
       </c>
-      <c r="F33" s="110"/>
-      <c r="G33" s="72"/>
+      <c r="F33" s="112"/>
+      <c r="G33" s="74"/>
       <c r="I33" s="1" t="s">
         <v>19</v>
       </c>
@@ -6067,8 +6073,8 @@
         <f t="shared" si="6"/>
         <v>0.70724999999999993</v>
       </c>
-      <c r="N33" s="110"/>
-      <c r="O33" s="72"/>
+      <c r="N33" s="112"/>
+      <c r="O33" s="74"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
@@ -6088,8 +6094,8 @@
         <f t="shared" si="4"/>
         <v>1.4489999999999998</v>
       </c>
-      <c r="F34" s="110"/>
-      <c r="G34" s="72"/>
+      <c r="F34" s="112"/>
+      <c r="G34" s="74"/>
       <c r="I34" s="1" t="s">
         <v>20</v>
       </c>
@@ -6107,8 +6113,8 @@
         <f t="shared" si="6"/>
         <v>1.4489999999999998</v>
       </c>
-      <c r="N34" s="110"/>
-      <c r="O34" s="72"/>
+      <c r="N34" s="112"/>
+      <c r="O34" s="74"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
@@ -6128,8 +6134,8 @@
         <f t="shared" si="4"/>
         <v>1.4489999999999998</v>
       </c>
-      <c r="F35" s="108"/>
-      <c r="G35" s="72"/>
+      <c r="F35" s="110"/>
+      <c r="G35" s="74"/>
       <c r="I35" s="1" t="s">
         <v>23</v>
       </c>
@@ -6147,8 +6153,8 @@
         <f t="shared" si="6"/>
         <v>6.1749999999999989</v>
       </c>
-      <c r="N35" s="110"/>
-      <c r="O35" s="72"/>
+      <c r="N35" s="112"/>
+      <c r="O35" s="74"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
@@ -6168,11 +6174,11 @@
         <f t="shared" si="4"/>
         <v>2.1</v>
       </c>
-      <c r="F36" s="107">
+      <c r="F36" s="109">
         <f>D32+D33+D34+D36+D37</f>
         <v>4.2640000000000002</v>
       </c>
-      <c r="G36" s="72">
+      <c r="G36" s="74">
         <v>3</v>
       </c>
       <c r="I36" s="1" t="s">
@@ -6192,8 +6198,8 @@
         <f t="shared" si="6"/>
         <v>4.0631500000000003</v>
       </c>
-      <c r="N36" s="110"/>
-      <c r="O36" s="72"/>
+      <c r="N36" s="112"/>
+      <c r="O36" s="74"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
@@ -6213,8 +6219,8 @@
         <f t="shared" si="4"/>
         <v>3.2249999999999996</v>
       </c>
-      <c r="F37" s="108"/>
-      <c r="G37" s="72"/>
+      <c r="F37" s="110"/>
+      <c r="G37" s="74"/>
       <c r="I37" s="1" t="s">
         <v>27</v>
       </c>
@@ -6232,8 +6238,8 @@
         <f t="shared" si="6"/>
         <v>6.1749999999999989</v>
       </c>
-      <c r="N37" s="110"/>
-      <c r="O37" s="72"/>
+      <c r="N37" s="112"/>
+      <c r="O37" s="74"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D38" s="6" t="s">
@@ -6264,8 +6270,8 @@
         <f t="shared" si="6"/>
         <v>1.0373999999999999</v>
       </c>
-      <c r="N38" s="108"/>
-      <c r="O38" s="72"/>
+      <c r="N38" s="110"/>
+      <c r="O38" s="74"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D39" s="6" t="s">
@@ -6310,21 +6316,21 @@
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A43" s="101" t="s">
+      <c r="A43" s="103" t="s">
         <v>29</v>
       </c>
-      <c r="B43" s="102"/>
-      <c r="C43" s="102"/>
-      <c r="D43" s="102"/>
-      <c r="E43" s="103"/>
-      <c r="I43" s="101" t="s">
+      <c r="B43" s="104"/>
+      <c r="C43" s="104"/>
+      <c r="D43" s="104"/>
+      <c r="E43" s="105"/>
+      <c r="I43" s="103" t="s">
         <v>30</v>
       </c>
-      <c r="J43" s="102"/>
-      <c r="K43" s="102"/>
-      <c r="L43" s="102"/>
-      <c r="M43" s="102"/>
-      <c r="N43" s="103"/>
+      <c r="J43" s="104"/>
+      <c r="K43" s="104"/>
+      <c r="L43" s="104"/>
+      <c r="M43" s="104"/>
+      <c r="N43" s="105"/>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
@@ -6395,7 +6401,7 @@
         <f t="shared" ref="M45:M49" si="7">L45*J45</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N45" s="104">
+      <c r="N45" s="106">
         <f>L45+L46+L47</f>
         <v>0.84000000000000008</v>
       </c>
@@ -6434,7 +6440,7 @@
         <f t="shared" si="7"/>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N46" s="105"/>
+      <c r="N46" s="107"/>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
@@ -6470,7 +6476,7 @@
         <f t="shared" si="7"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="N47" s="106"/>
+      <c r="N47" s="108"/>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
@@ -6506,7 +6512,7 @@
         <f t="shared" si="7"/>
         <v>0.68</v>
       </c>
-      <c r="N48" s="104">
+      <c r="N48" s="106">
         <f>L45+L46+L48+L49</f>
         <v>1.2400000000000002</v>
       </c>
@@ -6528,7 +6534,7 @@
         <f t="shared" si="7"/>
         <v>0.68</v>
       </c>
-      <c r="N49" s="106"/>
+      <c r="N49" s="108"/>
     </row>
   </sheetData>
   <mergeCells count="28">

--- a/dev_docs/千界万锻数值表格-26_4_21.xlsx
+++ b/dev_docs/千界万锻数值表格-26_4_21.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\AppData\Roaming\PrismLauncher\instances\SenDimsBanForges\minecraft\dev_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC49CA77-7BB2-470C-94C9-EE0CD95FB092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E5E0E68-B004-4077-B6A4-81133CBF0AC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-6720" windowWidth="30936" windowHeight="18816" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7665" yWindow="5055" windowWidth="26430" windowHeight="15435" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="数值分配" sheetId="3" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="210">
   <si>
     <t>最终攻击力=面板攻击+横扫之刃+评分等级+杀手附魔</t>
   </si>
@@ -859,6 +859,46 @@
   </si>
   <si>
     <t>下界合金碎片</t>
+  </si>
+  <si>
+    <t>凋零合金锭</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>娜迦鳞片</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>穹玉</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>太阳能板</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>充能器</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>巨型黑曜石</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>延迟器</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>耐热金属门</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>虚空核心</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>泰拉钢锭</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1527,16 +1567,91 @@
     <xf numFmtId="0" fontId="5" fillId="13" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="8" xfId="8" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1551,81 +1666,6 @@
     <xf numFmtId="0" fontId="0" fillId="25" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="8" xfId="8" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1635,6 +1675,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1644,19 +1696,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1988,57 +2028,57 @@
     </row>
     <row r="3" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C3" s="21"/>
-      <c r="D3" s="70" t="s">
+      <c r="D3" s="72" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
-      <c r="I3" s="70"/>
-      <c r="J3" s="70"/>
-      <c r="K3" s="70"/>
-      <c r="L3" s="70"/>
-      <c r="M3" s="70"/>
-      <c r="N3" s="70"/>
-      <c r="O3" s="70"/>
-      <c r="P3" s="70"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="72"/>
+      <c r="K3" s="72"/>
+      <c r="L3" s="72"/>
+      <c r="M3" s="72"/>
+      <c r="N3" s="72"/>
+      <c r="O3" s="72"/>
+      <c r="P3" s="72"/>
       <c r="Q3" s="21"/>
       <c r="R3" s="21"/>
       <c r="S3" s="21"/>
       <c r="T3" s="21"/>
-      <c r="V3" s="70" t="s">
+      <c r="V3" s="72" t="s">
         <v>52</v>
       </c>
-      <c r="W3" s="70"/>
-      <c r="X3" s="70"/>
-      <c r="Y3" s="70"/>
-      <c r="Z3" s="70"/>
-      <c r="AA3" s="70"/>
-      <c r="AB3" s="70"/>
-      <c r="AC3" s="70"/>
-      <c r="AD3" s="70"/>
-      <c r="AE3" s="70"/>
-      <c r="AF3" s="70"/>
-      <c r="AG3" s="70"/>
-      <c r="AH3" s="70"/>
-      <c r="AI3" s="70"/>
-      <c r="AJ3" s="70"/>
-      <c r="AK3" s="70"/>
-      <c r="AL3" s="70"/>
-      <c r="AM3" s="70"/>
-      <c r="AN3" s="70"/>
-      <c r="AO3" s="70"/>
-      <c r="AP3" s="70"/>
-      <c r="AQ3" s="70"/>
-      <c r="AR3" s="70"/>
-      <c r="AS3" s="70"/>
-      <c r="AT3" s="70"/>
-      <c r="AU3" s="70"/>
-      <c r="AV3" s="70"/>
-      <c r="AW3" s="70"/>
-      <c r="AX3" s="70"/>
-      <c r="AY3" s="70"/>
+      <c r="W3" s="72"/>
+      <c r="X3" s="72"/>
+      <c r="Y3" s="72"/>
+      <c r="Z3" s="72"/>
+      <c r="AA3" s="72"/>
+      <c r="AB3" s="72"/>
+      <c r="AC3" s="72"/>
+      <c r="AD3" s="72"/>
+      <c r="AE3" s="72"/>
+      <c r="AF3" s="72"/>
+      <c r="AG3" s="72"/>
+      <c r="AH3" s="72"/>
+      <c r="AI3" s="72"/>
+      <c r="AJ3" s="72"/>
+      <c r="AK3" s="72"/>
+      <c r="AL3" s="72"/>
+      <c r="AM3" s="72"/>
+      <c r="AN3" s="72"/>
+      <c r="AO3" s="72"/>
+      <c r="AP3" s="72"/>
+      <c r="AQ3" s="72"/>
+      <c r="AR3" s="72"/>
+      <c r="AS3" s="72"/>
+      <c r="AT3" s="72"/>
+      <c r="AU3" s="72"/>
+      <c r="AV3" s="72"/>
+      <c r="AW3" s="72"/>
+      <c r="AX3" s="72"/>
+      <c r="AY3" s="72"/>
       <c r="AZ3" s="21"/>
     </row>
     <row r="4" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
@@ -2084,44 +2124,44 @@
       <c r="R4" s="21"/>
       <c r="S4" s="21"/>
       <c r="T4" s="21"/>
-      <c r="V4" s="71" t="s">
+      <c r="V4" s="73" t="s">
         <v>57</v>
       </c>
-      <c r="W4" s="71"/>
-      <c r="X4" s="71"/>
-      <c r="Y4" s="71"/>
-      <c r="Z4" s="71"/>
-      <c r="AA4" s="71"/>
+      <c r="W4" s="73"/>
+      <c r="X4" s="73"/>
+      <c r="Y4" s="73"/>
+      <c r="Z4" s="73"/>
+      <c r="AA4" s="73"/>
       <c r="AB4" s="21"/>
       <c r="AC4" s="21"/>
-      <c r="AD4" s="71" t="s">
+      <c r="AD4" s="73" t="s">
         <v>59</v>
       </c>
-      <c r="AE4" s="71"/>
-      <c r="AF4" s="71"/>
-      <c r="AG4" s="71"/>
+      <c r="AE4" s="73"/>
+      <c r="AF4" s="73"/>
+      <c r="AG4" s="73"/>
       <c r="AH4" s="21"/>
       <c r="AI4" s="21"/>
       <c r="AJ4" s="21"/>
       <c r="AK4" s="21"/>
-      <c r="AL4" s="71" t="s">
+      <c r="AL4" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="AM4" s="71"/>
-      <c r="AN4" s="71"/>
-      <c r="AO4" s="71"/>
-      <c r="AP4" s="71"/>
-      <c r="AQ4" s="71"/>
+      <c r="AM4" s="73"/>
+      <c r="AN4" s="73"/>
+      <c r="AO4" s="73"/>
+      <c r="AP4" s="73"/>
+      <c r="AQ4" s="73"/>
       <c r="AR4" s="21"/>
       <c r="AS4" s="21"/>
-      <c r="AT4" s="71" t="s">
+      <c r="AT4" s="73" t="s">
         <v>61</v>
       </c>
-      <c r="AU4" s="71"/>
-      <c r="AV4" s="71"/>
-      <c r="AW4" s="71"/>
-      <c r="AX4" s="71"/>
-      <c r="AY4" s="71"/>
+      <c r="AU4" s="73"/>
+      <c r="AV4" s="73"/>
+      <c r="AW4" s="73"/>
+      <c r="AX4" s="73"/>
+      <c r="AY4" s="73"/>
       <c r="AZ4" s="21"/>
     </row>
     <row r="5" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
@@ -2263,7 +2303,7 @@
       </c>
     </row>
     <row r="6" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B6" s="72">
+      <c r="B6" s="70">
         <v>0</v>
       </c>
       <c r="C6" s="19">
@@ -2427,7 +2467,7 @@
       </c>
     </row>
     <row r="7" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B7" s="72"/>
+      <c r="B7" s="70"/>
       <c r="C7" s="19">
         <v>1.1000000000000001</v>
       </c>
@@ -2589,7 +2629,7 @@
       </c>
     </row>
     <row r="8" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B8" s="72">
+      <c r="B8" s="70">
         <v>1</v>
       </c>
       <c r="C8" s="18">
@@ -2753,7 +2793,7 @@
       </c>
     </row>
     <row r="9" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="72"/>
+      <c r="B9" s="70"/>
       <c r="C9" s="19">
         <v>1.3</v>
       </c>
@@ -2915,7 +2955,7 @@
       </c>
     </row>
     <row r="10" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B10" s="73">
+      <c r="B10" s="71">
         <v>2</v>
       </c>
       <c r="C10" s="18">
@@ -3079,10 +3119,10 @@
       </c>
     </row>
     <row r="11" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B11" s="73"/>
+      <c r="B11" s="71"/>
     </row>
     <row r="12" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="73"/>
+      <c r="B12" s="71"/>
       <c r="C12" s="19">
         <v>2.1</v>
       </c>
@@ -3244,7 +3284,7 @@
       </c>
     </row>
     <row r="13" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B13" s="72">
+      <c r="B13" s="70">
         <v>3</v>
       </c>
       <c r="C13" s="18">
@@ -3408,7 +3448,7 @@
       </c>
     </row>
     <row r="14" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B14" s="72"/>
+      <c r="B14" s="70"/>
       <c r="C14" s="19">
         <v>2.2999999999999998</v>
       </c>
@@ -3570,7 +3610,7 @@
       </c>
     </row>
     <row r="16" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="72">
+      <c r="B16" s="70">
         <v>4</v>
       </c>
       <c r="C16" s="19">
@@ -3734,7 +3774,7 @@
       </c>
     </row>
     <row r="17" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="72"/>
+      <c r="B17" s="70"/>
       <c r="C17" s="18">
         <v>3.2</v>
       </c>
@@ -3896,7 +3936,7 @@
       </c>
     </row>
     <row r="18" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="72"/>
+      <c r="B18" s="70"/>
       <c r="C18" s="19">
         <v>3.3</v>
       </c>
@@ -4058,7 +4098,7 @@
       </c>
     </row>
     <row r="20" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="72">
+      <c r="B20" s="70">
         <v>5</v>
       </c>
       <c r="C20" s="18">
@@ -4222,7 +4262,7 @@
       </c>
     </row>
     <row r="21" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="72"/>
+      <c r="B21" s="70"/>
       <c r="C21" s="19">
         <v>4.2</v>
       </c>
@@ -4385,18 +4425,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="D3:P3"/>
+    <mergeCell ref="V3:AY3"/>
+    <mergeCell ref="AT4:AY4"/>
+    <mergeCell ref="AL4:AQ4"/>
+    <mergeCell ref="AD4:AG4"/>
+    <mergeCell ref="V4:AA4"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="B10:B12"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="B16:B18"/>
-    <mergeCell ref="D3:P3"/>
-    <mergeCell ref="V3:AY3"/>
-    <mergeCell ref="AT4:AY4"/>
-    <mergeCell ref="AL4:AQ4"/>
-    <mergeCell ref="AD4:AG4"/>
-    <mergeCell ref="V4:AA4"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4423,30 +4463,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E1" s="84" t="s">
+      <c r="E1" s="74" t="s">
         <v>96</v>
       </c>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
       <c r="I1" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="K1" s="85" t="s">
+      <c r="K1" s="75" t="s">
         <v>97</v>
       </c>
-      <c r="L1" s="85"/>
-      <c r="M1" s="85"/>
-      <c r="N1" s="85"/>
+      <c r="L1" s="75"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="75"/>
       <c r="O1" s="38" t="s">
         <v>159</v>
       </c>
-      <c r="Q1" s="86" t="s">
+      <c r="Q1" s="76" t="s">
         <v>98</v>
       </c>
-      <c r="R1" s="86"/>
-      <c r="S1" s="86"/>
-      <c r="T1" s="86"/>
+      <c r="R1" s="76"/>
+      <c r="S1" s="76"/>
+      <c r="T1" s="76"/>
       <c r="U1" s="39" t="s">
         <v>159</v>
       </c>
@@ -4455,35 +4495,35 @@
       <c r="A2" s="40" t="s">
         <v>158</v>
       </c>
-      <c r="B2" s="87" t="s">
+      <c r="B2" s="77" t="s">
         <v>157</v>
       </c>
-      <c r="C2" s="87"/>
-      <c r="D2" s="87"/>
-      <c r="E2" s="102" t="s">
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="92" t="s">
         <v>196</v>
       </c>
-      <c r="F2" s="102"/>
-      <c r="G2" s="102" t="s">
+      <c r="F2" s="92"/>
+      <c r="G2" s="92" t="s">
         <v>197</v>
       </c>
-      <c r="H2" s="102"/>
-      <c r="K2" s="102" t="s">
+      <c r="H2" s="92"/>
+      <c r="K2" s="92" t="s">
         <v>196</v>
       </c>
-      <c r="L2" s="102"/>
-      <c r="M2" s="102" t="s">
+      <c r="L2" s="92"/>
+      <c r="M2" s="92" t="s">
         <v>197</v>
       </c>
-      <c r="N2" s="102"/>
-      <c r="Q2" s="102" t="s">
+      <c r="N2" s="92"/>
+      <c r="Q2" s="92" t="s">
         <v>196</v>
       </c>
-      <c r="R2" s="102"/>
-      <c r="S2" s="102" t="s">
+      <c r="R2" s="92"/>
+      <c r="S2" s="92" t="s">
         <v>197</v>
       </c>
-      <c r="T2" s="102"/>
+      <c r="T2" s="92"/>
     </row>
     <row r="3" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="41">
@@ -4496,25 +4536,25 @@
         <v>122</v>
       </c>
       <c r="D3" s="1"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="90"/>
-      <c r="I3" s="100" t="s">
+      <c r="E3" s="78"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="90" t="s">
         <v>129</v>
       </c>
-      <c r="K3" s="88"/>
-      <c r="L3" s="89"/>
-      <c r="M3" s="89"/>
-      <c r="N3" s="90"/>
+      <c r="K3" s="78"/>
+      <c r="L3" s="79"/>
+      <c r="M3" s="79"/>
+      <c r="N3" s="80"/>
       <c r="O3" s="45" t="s">
         <v>129</v>
       </c>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="89"/>
-      <c r="S3" s="89"/>
-      <c r="T3" s="90"/>
-      <c r="U3" s="82" t="s">
+      <c r="Q3" s="78"/>
+      <c r="R3" s="79"/>
+      <c r="S3" s="79"/>
+      <c r="T3" s="80"/>
+      <c r="U3" s="97" t="s">
         <v>156</v>
       </c>
     </row>
@@ -4527,11 +4567,11 @@
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="91"/>
-      <c r="F4" s="92"/>
-      <c r="G4" s="92"/>
-      <c r="H4" s="93"/>
-      <c r="I4" s="101"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="83"/>
+      <c r="I4" s="91"/>
       <c r="K4" s="49" t="s">
         <v>133</v>
       </c>
@@ -4540,14 +4580,14 @@
         <v>134</v>
       </c>
       <c r="N4" s="47"/>
-      <c r="O4" s="97">
+      <c r="O4" s="87">
         <v>0</v>
       </c>
-      <c r="Q4" s="94"/>
-      <c r="R4" s="95"/>
-      <c r="S4" s="95"/>
-      <c r="T4" s="96"/>
-      <c r="U4" s="83"/>
+      <c r="Q4" s="84"/>
+      <c r="R4" s="85"/>
+      <c r="S4" s="85"/>
+      <c r="T4" s="86"/>
+      <c r="U4" s="98"/>
     </row>
     <row r="5" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="42">
@@ -4574,7 +4614,7 @@
       <c r="H5" s="48" t="s">
         <v>132</v>
       </c>
-      <c r="I5" s="77">
+      <c r="I5" s="102">
         <v>0</v>
       </c>
       <c r="K5" s="48" t="s">
@@ -4585,12 +4625,12 @@
         <v>194</v>
       </c>
       <c r="N5" s="47"/>
-      <c r="O5" s="98"/>
-      <c r="Q5" s="94"/>
-      <c r="R5" s="95"/>
-      <c r="S5" s="95"/>
-      <c r="T5" s="96"/>
-      <c r="U5" s="83"/>
+      <c r="O5" s="88"/>
+      <c r="Q5" s="84"/>
+      <c r="R5" s="85"/>
+      <c r="S5" s="85"/>
+      <c r="T5" s="86"/>
+      <c r="U5" s="98"/>
     </row>
     <row r="6" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="42">
@@ -4607,19 +4647,19 @@
         <v>160</v>
       </c>
       <c r="H6" s="47"/>
-      <c r="I6" s="77"/>
+      <c r="I6" s="102"/>
       <c r="K6" s="48" t="s">
         <v>165</v>
       </c>
       <c r="L6" s="48"/>
       <c r="M6" s="48"/>
       <c r="N6" s="47"/>
-      <c r="O6" s="98"/>
-      <c r="Q6" s="91"/>
-      <c r="R6" s="92"/>
-      <c r="S6" s="92"/>
-      <c r="T6" s="93"/>
-      <c r="U6" s="83"/>
+      <c r="O6" s="88"/>
+      <c r="Q6" s="81"/>
+      <c r="R6" s="82"/>
+      <c r="S6" s="82"/>
+      <c r="T6" s="83"/>
+      <c r="U6" s="98"/>
     </row>
     <row r="7" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="42">
@@ -4640,7 +4680,7 @@
         <v>164</v>
       </c>
       <c r="H7" s="47"/>
-      <c r="I7" s="77"/>
+      <c r="I7" s="102"/>
       <c r="K7" s="48" t="s">
         <v>167</v>
       </c>
@@ -4649,7 +4689,7 @@
         <v>166</v>
       </c>
       <c r="N7" s="47"/>
-      <c r="O7" s="99"/>
+      <c r="O7" s="89"/>
       <c r="Q7" s="54" t="s">
         <v>199</v>
       </c>
@@ -4662,7 +4702,7 @@
       <c r="T7" s="51" t="s">
         <v>173</v>
       </c>
-      <c r="U7" s="78">
+      <c r="U7" s="93">
         <v>1</v>
       </c>
     </row>
@@ -4687,7 +4727,7 @@
         <v>169</v>
       </c>
       <c r="H8" s="47"/>
-      <c r="I8" s="77"/>
+      <c r="I8" s="102"/>
       <c r="K8" s="53" t="s">
         <v>136</v>
       </c>
@@ -4700,7 +4740,7 @@
       <c r="N8" s="51" t="s">
         <v>170</v>
       </c>
-      <c r="O8" s="78">
+      <c r="O8" s="93">
         <v>1</v>
       </c>
       <c r="Q8" s="51" t="s">
@@ -4713,7 +4753,7 @@
       <c r="T8" s="51" t="s">
         <v>198</v>
       </c>
-      <c r="U8" s="78"/>
+      <c r="U8" s="93"/>
     </row>
     <row r="9" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="43">
@@ -4738,7 +4778,7 @@
       <c r="H9" s="50" t="s">
         <v>139</v>
       </c>
-      <c r="I9" s="78">
+      <c r="I9" s="93">
         <v>1</v>
       </c>
       <c r="K9" s="51" t="s">
@@ -4753,7 +4793,7 @@
       <c r="N9" s="51" t="s">
         <v>179</v>
       </c>
-      <c r="O9" s="78"/>
+      <c r="O9" s="93"/>
       <c r="Q9" s="33" t="s">
         <v>180</v>
       </c>
@@ -4762,7 +4802,7 @@
         <v>181</v>
       </c>
       <c r="T9" s="56"/>
-      <c r="U9" s="79">
+      <c r="U9" s="94">
         <v>2</v>
       </c>
     </row>
@@ -4781,7 +4821,7 @@
       <c r="F10" s="52"/>
       <c r="G10" s="52"/>
       <c r="H10" s="52"/>
-      <c r="I10" s="78"/>
+      <c r="I10" s="93"/>
       <c r="K10" s="57" t="s">
         <v>141</v>
       </c>
@@ -4792,7 +4832,7 @@
       <c r="N10" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="O10" s="79">
+      <c r="O10" s="94">
         <v>2</v>
       </c>
       <c r="Q10" s="33" t="s">
@@ -4801,7 +4841,7 @@
       <c r="R10" s="56"/>
       <c r="S10" s="56"/>
       <c r="T10" s="56"/>
-      <c r="U10" s="79"/>
+      <c r="U10" s="94"/>
     </row>
     <row r="11" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="65">
@@ -4824,7 +4864,7 @@
       <c r="H11" s="55" t="s">
         <v>145</v>
       </c>
-      <c r="I11" s="79">
+      <c r="I11" s="94">
         <v>2</v>
       </c>
       <c r="K11" s="33"/>
@@ -4833,7 +4873,7 @@
         <v>184</v>
       </c>
       <c r="N11" s="56"/>
-      <c r="O11" s="79"/>
+      <c r="O11" s="94"/>
       <c r="Q11" s="61" t="s">
         <v>183</v>
       </c>
@@ -4842,7 +4882,7 @@
         <v>185</v>
       </c>
       <c r="T11" s="59"/>
-      <c r="U11" s="80">
+      <c r="U11" s="95">
         <v>3</v>
       </c>
     </row>
@@ -4863,21 +4903,21 @@
         <v>186</v>
       </c>
       <c r="H12" s="56"/>
-      <c r="I12" s="79"/>
+      <c r="I12" s="94"/>
       <c r="K12" s="33"/>
       <c r="L12" s="56"/>
       <c r="M12" s="33" t="s">
         <v>187</v>
       </c>
       <c r="N12" s="56"/>
-      <c r="O12" s="79"/>
+      <c r="O12" s="94"/>
       <c r="Q12" s="69" t="s">
         <v>152</v>
       </c>
       <c r="R12" s="59"/>
       <c r="S12" s="59"/>
       <c r="T12" s="59"/>
-      <c r="U12" s="80"/>
+      <c r="U12" s="95"/>
     </row>
     <row r="13" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="65">
@@ -4898,7 +4938,7 @@
       <c r="F13" s="33"/>
       <c r="G13" s="33"/>
       <c r="H13" s="56"/>
-      <c r="I13" s="79"/>
+      <c r="I13" s="94"/>
       <c r="K13" s="60" t="s">
         <v>146</v>
       </c>
@@ -4922,7 +4962,7 @@
       </c>
       <c r="S13" s="63"/>
       <c r="T13" s="63"/>
-      <c r="U13" s="81">
+      <c r="U13" s="96">
         <v>4</v>
       </c>
     </row>
@@ -4943,7 +4983,7 @@
       <c r="F14" s="58"/>
       <c r="G14" s="61"/>
       <c r="H14" s="59"/>
-      <c r="I14" s="80">
+      <c r="I14" s="95">
         <v>3</v>
       </c>
       <c r="K14" s="62"/>
@@ -4952,7 +4992,7 @@
         <v>148</v>
       </c>
       <c r="N14" s="63"/>
-      <c r="O14" s="75">
+      <c r="O14" s="100">
         <v>4</v>
       </c>
       <c r="Q14" s="67" t="s">
@@ -4961,7 +5001,7 @@
       <c r="R14" s="63"/>
       <c r="S14" s="63"/>
       <c r="T14" s="63"/>
-      <c r="U14" s="81"/>
+      <c r="U14" s="96"/>
     </row>
     <row r="15" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="44">
@@ -4978,14 +5018,14 @@
       <c r="F15" s="59"/>
       <c r="G15" s="59"/>
       <c r="H15" s="59"/>
-      <c r="I15" s="80"/>
+      <c r="I15" s="95"/>
       <c r="K15" s="62"/>
       <c r="L15" s="63"/>
       <c r="M15" s="28" t="s">
         <v>151</v>
       </c>
       <c r="N15" s="63"/>
-      <c r="O15" s="76"/>
+      <c r="O15" s="101"/>
       <c r="Q15" s="68" t="s">
         <v>152</v>
       </c>
@@ -4996,13 +5036,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C18" s="74" t="s">
+    <row r="18" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C18" s="99" t="s">
         <v>99</v>
       </c>
-      <c r="D18" s="74"/>
-    </row>
-    <row r="19" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D18" s="99"/>
+    </row>
+    <row r="19" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="3" t="s">
         <v>100</v>
       </c>
@@ -5013,7 +5053,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="20" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="3" t="s">
         <v>124</v>
       </c>
@@ -5023,8 +5063,20 @@
       <c r="D20" s="3">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="21" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E20" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="3" t="s">
         <v>125</v>
       </c>
@@ -5034,8 +5086,20 @@
       <c r="D21" s="1">
         <v>1.4</v>
       </c>
-    </row>
-    <row r="22" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E21" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="3" t="s">
         <v>126</v>
       </c>
@@ -5045,8 +5109,14 @@
       <c r="D22" s="1">
         <v>2.2999999999999998</v>
       </c>
-    </row>
-    <row r="23" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E22" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="3" t="s">
         <v>127</v>
       </c>
@@ -5056,8 +5126,14 @@
       <c r="D23" s="1">
         <v>3.3</v>
       </c>
-    </row>
-    <row r="24" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E23" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="3" t="s">
         <v>128</v>
       </c>
@@ -5067,9 +5143,28 @@
       <c r="D24" s="3" t="s">
         <v>129</v>
       </c>
+      <c r="E24" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>152</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="O14:O15"/>
+    <mergeCell ref="I5:I8"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I11:I13"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="O10:O12"/>
+    <mergeCell ref="U7:U8"/>
+    <mergeCell ref="U9:U10"/>
+    <mergeCell ref="U11:U12"/>
+    <mergeCell ref="U13:U14"/>
+    <mergeCell ref="U3:U6"/>
     <mergeCell ref="E1:H1"/>
     <mergeCell ref="K1:N1"/>
     <mergeCell ref="Q1:T1"/>
@@ -5085,19 +5180,6 @@
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="K2:L2"/>
-    <mergeCell ref="U7:U8"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="U11:U12"/>
-    <mergeCell ref="U13:U14"/>
-    <mergeCell ref="U3:U6"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="O14:O15"/>
-    <mergeCell ref="I5:I8"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I11:I13"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="O10:O12"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5114,32 +5196,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="109" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="113"/>
-      <c r="C1" s="113"/>
-      <c r="D1" s="113"/>
-      <c r="E1" s="113"/>
-      <c r="G1" s="113" t="s">
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="G1" s="109" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="113"/>
-      <c r="I1" s="113"/>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
-      <c r="V1" s="113"/>
-      <c r="W1" s="113"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
+      <c r="V1" s="109"/>
+      <c r="W1" s="109"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
@@ -5312,11 +5394,11 @@
         <f t="shared" ref="E10:E15" si="0">D10*B10</f>
         <v>0.5</v>
       </c>
-      <c r="F10" s="109">
+      <c r="F10" s="106">
         <f>D10+D11+D12+D13</f>
         <v>2</v>
       </c>
-      <c r="G10" s="74">
+      <c r="G10" s="99">
         <v>1.5</v>
       </c>
       <c r="I10" s="1" t="s">
@@ -5336,11 +5418,11 @@
         <f t="shared" ref="M10:M16" si="2">L10*J10</f>
         <v>0.5</v>
       </c>
-      <c r="N10" s="109">
+      <c r="N10" s="106">
         <f>L10+L11+L12+L13+L14+L15+L16</f>
         <v>3.5</v>
       </c>
-      <c r="O10" s="74">
+      <c r="O10" s="99">
         <v>4</v>
       </c>
       <c r="Q10" s="1" t="s">
@@ -5360,7 +5442,7 @@
         <f>T10*R10</f>
         <v>0.5</v>
       </c>
-      <c r="V10" s="106">
+      <c r="V10" s="110">
         <f>T10+T11+T12</f>
         <v>1.84</v>
       </c>
@@ -5383,8 +5465,8 @@
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="F11" s="112"/>
-      <c r="G11" s="74"/>
+      <c r="F11" s="107"/>
+      <c r="G11" s="99"/>
       <c r="I11" s="1" t="s">
         <v>19</v>
       </c>
@@ -5402,8 +5484,8 @@
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
-      <c r="N11" s="112"/>
-      <c r="O11" s="74"/>
+      <c r="N11" s="107"/>
+      <c r="O11" s="99"/>
       <c r="Q11" s="1" t="s">
         <v>19</v>
       </c>
@@ -5421,7 +5503,7 @@
         <f>T11*R11</f>
         <v>0.5</v>
       </c>
-      <c r="V11" s="107"/>
+      <c r="V11" s="111"/>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
@@ -5441,8 +5523,8 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F12" s="112"/>
-      <c r="G12" s="74"/>
+      <c r="F12" s="107"/>
+      <c r="G12" s="99"/>
       <c r="I12" s="1" t="s">
         <v>20</v>
       </c>
@@ -5460,8 +5542,8 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="N12" s="112"/>
-      <c r="O12" s="74"/>
+      <c r="N12" s="107"/>
+      <c r="O12" s="99"/>
       <c r="Q12" s="1" t="s">
         <v>21</v>
       </c>
@@ -5479,7 +5561,7 @@
         <f>T12*R12</f>
         <v>1.6800000000000002</v>
       </c>
-      <c r="V12" s="108"/>
+      <c r="V12" s="112"/>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
@@ -5499,8 +5581,8 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F13" s="110"/>
-      <c r="G13" s="74"/>
+      <c r="F13" s="108"/>
+      <c r="G13" s="99"/>
       <c r="I13" s="1" t="s">
         <v>23</v>
       </c>
@@ -5518,8 +5600,8 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="N13" s="112"/>
-      <c r="O13" s="74"/>
+      <c r="N13" s="107"/>
+      <c r="O13" s="99"/>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
@@ -5539,11 +5621,11 @@
         <f t="shared" si="0"/>
         <v>1.575</v>
       </c>
-      <c r="F14" s="109">
+      <c r="F14" s="106">
         <f>D10+D11+D12+D14+D15</f>
         <v>3.09375</v>
       </c>
-      <c r="G14" s="74">
+      <c r="G14" s="99">
         <v>3</v>
       </c>
       <c r="I14" s="1" t="s">
@@ -5563,8 +5645,8 @@
         <f t="shared" si="2"/>
         <v>3.5</v>
       </c>
-      <c r="N14" s="112"/>
-      <c r="O14" s="74"/>
+      <c r="N14" s="107"/>
+      <c r="O14" s="99"/>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
@@ -5584,8 +5666,8 @@
         <f t="shared" si="0"/>
         <v>2.4187500000000002</v>
       </c>
-      <c r="F15" s="110"/>
-      <c r="G15" s="74"/>
+      <c r="F15" s="108"/>
+      <c r="G15" s="99"/>
       <c r="I15" s="1" t="s">
         <v>27</v>
       </c>
@@ -5603,8 +5685,8 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="N15" s="112"/>
-      <c r="O15" s="74"/>
+      <c r="N15" s="107"/>
+      <c r="O15" s="99"/>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.15">
       <c r="D16" s="6" t="s">
@@ -5635,8 +5717,8 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="N16" s="110"/>
-      <c r="O16" s="74"/>
+      <c r="N16" s="108"/>
+      <c r="O16" s="99"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D17" s="6" t="s">
@@ -5772,7 +5854,7 @@
         <f t="shared" ref="M22:M26" si="3">L22*J22</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N22" s="106">
+      <c r="N22" s="110">
         <f>L22+L23+L24</f>
         <v>0.84000000000000008</v>
       </c>
@@ -5812,7 +5894,7 @@
         <f t="shared" si="3"/>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N23" s="107"/>
+      <c r="N23" s="111"/>
       <c r="O23" s="5"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.15">
@@ -5849,7 +5931,7 @@
         <f t="shared" si="3"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="N24" s="108"/>
+      <c r="N24" s="112"/>
       <c r="O24" s="5"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.15">
@@ -5886,7 +5968,7 @@
         <f t="shared" si="3"/>
         <v>0.68</v>
       </c>
-      <c r="N25" s="106">
+      <c r="N25" s="110">
         <f>L22+L23+L25+L26</f>
         <v>1.2400000000000002</v>
       </c>
@@ -5909,7 +5991,7 @@
         <f t="shared" si="3"/>
         <v>0.68</v>
       </c>
-      <c r="N26" s="108"/>
+      <c r="N26" s="112"/>
       <c r="O26" s="5"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.15">
@@ -5923,7 +6005,7 @@
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A30" s="111" t="s">
+      <c r="A30" s="113" t="s">
         <v>43</v>
       </c>
       <c r="B30" s="104"/>
@@ -5932,7 +6014,7 @@
       <c r="E30" s="104"/>
       <c r="F30" s="105"/>
       <c r="G30" s="4"/>
-      <c r="I30" s="111" t="s">
+      <c r="I30" s="113" t="s">
         <v>44</v>
       </c>
       <c r="J30" s="104"/>
@@ -6004,11 +6086,11 @@
         <f t="shared" ref="E32:E37" si="4">D32*B32</f>
         <v>0.70724999999999993</v>
       </c>
-      <c r="F32" s="109">
+      <c r="F32" s="106">
         <f>D32+D33+D34+D35</f>
         <v>2.8634999999999997</v>
       </c>
-      <c r="G32" s="74">
+      <c r="G32" s="99">
         <v>1.5</v>
       </c>
       <c r="I32" s="1" t="s">
@@ -6028,11 +6110,11 @@
         <f t="shared" ref="M32:M38" si="6">L32*J32</f>
         <v>0.70724999999999993</v>
       </c>
-      <c r="N32" s="109">
+      <c r="N32" s="106">
         <f>L32+L33+L34+L35+L36+L37+L38</f>
         <v>4.4731499999999995</v>
       </c>
-      <c r="O32" s="74">
+      <c r="O32" s="99">
         <v>4</v>
       </c>
     </row>
@@ -6054,8 +6136,8 @@
         <f t="shared" si="4"/>
         <v>0.70724999999999993</v>
       </c>
-      <c r="F33" s="112"/>
-      <c r="G33" s="74"/>
+      <c r="F33" s="107"/>
+      <c r="G33" s="99"/>
       <c r="I33" s="1" t="s">
         <v>19</v>
       </c>
@@ -6073,8 +6155,8 @@
         <f t="shared" si="6"/>
         <v>0.70724999999999993</v>
       </c>
-      <c r="N33" s="112"/>
-      <c r="O33" s="74"/>
+      <c r="N33" s="107"/>
+      <c r="O33" s="99"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
@@ -6094,8 +6176,8 @@
         <f t="shared" si="4"/>
         <v>1.4489999999999998</v>
       </c>
-      <c r="F34" s="112"/>
-      <c r="G34" s="74"/>
+      <c r="F34" s="107"/>
+      <c r="G34" s="99"/>
       <c r="I34" s="1" t="s">
         <v>20</v>
       </c>
@@ -6113,8 +6195,8 @@
         <f t="shared" si="6"/>
         <v>1.4489999999999998</v>
       </c>
-      <c r="N34" s="112"/>
-      <c r="O34" s="74"/>
+      <c r="N34" s="107"/>
+      <c r="O34" s="99"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
@@ -6134,8 +6216,8 @@
         <f t="shared" si="4"/>
         <v>1.4489999999999998</v>
       </c>
-      <c r="F35" s="110"/>
-      <c r="G35" s="74"/>
+      <c r="F35" s="108"/>
+      <c r="G35" s="99"/>
       <c r="I35" s="1" t="s">
         <v>23</v>
       </c>
@@ -6153,8 +6235,8 @@
         <f t="shared" si="6"/>
         <v>6.1749999999999989</v>
       </c>
-      <c r="N35" s="112"/>
-      <c r="O35" s="74"/>
+      <c r="N35" s="107"/>
+      <c r="O35" s="99"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
@@ -6174,11 +6256,11 @@
         <f t="shared" si="4"/>
         <v>2.1</v>
       </c>
-      <c r="F36" s="109">
+      <c r="F36" s="106">
         <f>D32+D33+D34+D36+D37</f>
         <v>4.2640000000000002</v>
       </c>
-      <c r="G36" s="74">
+      <c r="G36" s="99">
         <v>3</v>
       </c>
       <c r="I36" s="1" t="s">
@@ -6198,8 +6280,8 @@
         <f t="shared" si="6"/>
         <v>4.0631500000000003</v>
       </c>
-      <c r="N36" s="112"/>
-      <c r="O36" s="74"/>
+      <c r="N36" s="107"/>
+      <c r="O36" s="99"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
@@ -6219,8 +6301,8 @@
         <f t="shared" si="4"/>
         <v>3.2249999999999996</v>
       </c>
-      <c r="F37" s="110"/>
-      <c r="G37" s="74"/>
+      <c r="F37" s="108"/>
+      <c r="G37" s="99"/>
       <c r="I37" s="1" t="s">
         <v>27</v>
       </c>
@@ -6238,8 +6320,8 @@
         <f t="shared" si="6"/>
         <v>6.1749999999999989</v>
       </c>
-      <c r="N37" s="112"/>
-      <c r="O37" s="74"/>
+      <c r="N37" s="107"/>
+      <c r="O37" s="99"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D38" s="6" t="s">
@@ -6270,8 +6352,8 @@
         <f t="shared" si="6"/>
         <v>1.0373999999999999</v>
       </c>
-      <c r="N38" s="110"/>
-      <c r="O38" s="74"/>
+      <c r="N38" s="108"/>
+      <c r="O38" s="99"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D39" s="6" t="s">
@@ -6401,7 +6483,7 @@
         <f t="shared" ref="M45:M49" si="7">L45*J45</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N45" s="106">
+      <c r="N45" s="110">
         <f>L45+L46+L47</f>
         <v>0.84000000000000008</v>
       </c>
@@ -6440,7 +6522,7 @@
         <f t="shared" si="7"/>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N46" s="107"/>
+      <c r="N46" s="111"/>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
@@ -6476,7 +6558,7 @@
         <f t="shared" si="7"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="N47" s="108"/>
+      <c r="N47" s="112"/>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
@@ -6512,7 +6594,7 @@
         <f t="shared" si="7"/>
         <v>0.68</v>
       </c>
-      <c r="N48" s="106">
+      <c r="N48" s="110">
         <f>L45+L46+L48+L49</f>
         <v>1.2400000000000002</v>
       </c>
@@ -6534,10 +6616,29 @@
         <f t="shared" si="7"/>
         <v>0.68</v>
       </c>
-      <c r="N49" s="108"/>
+      <c r="N49" s="112"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="I43:N43"/>
+    <mergeCell ref="N45:N47"/>
+    <mergeCell ref="N48:N49"/>
+    <mergeCell ref="O32:O38"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="I30:N30"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="G32:G35"/>
+    <mergeCell ref="N32:N38"/>
+    <mergeCell ref="N22:N24"/>
+    <mergeCell ref="N25:N26"/>
+    <mergeCell ref="V10:V12"/>
+    <mergeCell ref="G10:G13"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="O10:O16"/>
+    <mergeCell ref="N10:N16"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="I20:N20"/>
     <mergeCell ref="F10:F13"/>
@@ -6547,25 +6648,6 @@
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="I8:N8"/>
     <mergeCell ref="Q8:V8"/>
-    <mergeCell ref="N22:N24"/>
-    <mergeCell ref="N25:N26"/>
-    <mergeCell ref="V10:V12"/>
-    <mergeCell ref="G10:G13"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="O10:O16"/>
-    <mergeCell ref="N10:N16"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="I30:N30"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="G32:G35"/>
-    <mergeCell ref="N32:N38"/>
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="I43:N43"/>
-    <mergeCell ref="N45:N47"/>
-    <mergeCell ref="N48:N49"/>
-    <mergeCell ref="O32:O38"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dev_docs/千界万锻数值表格-26_4_21.xlsx
+++ b/dev_docs/千界万锻数值表格-26_4_21.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\AppData\Roaming\PrismLauncher\instances\SenDimsBanForges\minecraft\dev_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E5E0E68-B004-4077-B6A4-81133CBF0AC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75B67A8F-D0B5-42E0-ACAF-394BBC266FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7665" yWindow="5055" windowWidth="26430" windowHeight="15435" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-6720" windowWidth="30936" windowHeight="18816" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="数值分配" sheetId="3" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="214">
   <si>
     <t>最终攻击力=面板攻击+横扫之刃+评分等级+杀手附魔</t>
   </si>
@@ -898,6 +898,22 @@
   </si>
   <si>
     <t>泰拉钢锭</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>元素瓶</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>等级</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>固定</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>百分比</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1356,7 +1372,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1567,16 +1583,46 @@
     <xf numFmtId="0" fontId="5" fillId="13" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
@@ -1636,36 +1682,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1675,28 +1691,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2028,57 +2047,57 @@
     </row>
     <row r="3" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C3" s="21"/>
-      <c r="D3" s="72" t="s">
+      <c r="D3" s="70" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="72"/>
-      <c r="K3" s="72"/>
-      <c r="L3" s="72"/>
-      <c r="M3" s="72"/>
-      <c r="N3" s="72"/>
-      <c r="O3" s="72"/>
-      <c r="P3" s="72"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="70"/>
+      <c r="I3" s="70"/>
+      <c r="J3" s="70"/>
+      <c r="K3" s="70"/>
+      <c r="L3" s="70"/>
+      <c r="M3" s="70"/>
+      <c r="N3" s="70"/>
+      <c r="O3" s="70"/>
+      <c r="P3" s="70"/>
       <c r="Q3" s="21"/>
       <c r="R3" s="21"/>
       <c r="S3" s="21"/>
       <c r="T3" s="21"/>
-      <c r="V3" s="72" t="s">
+      <c r="V3" s="70" t="s">
         <v>52</v>
       </c>
-      <c r="W3" s="72"/>
-      <c r="X3" s="72"/>
-      <c r="Y3" s="72"/>
-      <c r="Z3" s="72"/>
-      <c r="AA3" s="72"/>
-      <c r="AB3" s="72"/>
-      <c r="AC3" s="72"/>
-      <c r="AD3" s="72"/>
-      <c r="AE3" s="72"/>
-      <c r="AF3" s="72"/>
-      <c r="AG3" s="72"/>
-      <c r="AH3" s="72"/>
-      <c r="AI3" s="72"/>
-      <c r="AJ3" s="72"/>
-      <c r="AK3" s="72"/>
-      <c r="AL3" s="72"/>
-      <c r="AM3" s="72"/>
-      <c r="AN3" s="72"/>
-      <c r="AO3" s="72"/>
-      <c r="AP3" s="72"/>
-      <c r="AQ3" s="72"/>
-      <c r="AR3" s="72"/>
-      <c r="AS3" s="72"/>
-      <c r="AT3" s="72"/>
-      <c r="AU3" s="72"/>
-      <c r="AV3" s="72"/>
-      <c r="AW3" s="72"/>
-      <c r="AX3" s="72"/>
-      <c r="AY3" s="72"/>
+      <c r="W3" s="70"/>
+      <c r="X3" s="70"/>
+      <c r="Y3" s="70"/>
+      <c r="Z3" s="70"/>
+      <c r="AA3" s="70"/>
+      <c r="AB3" s="70"/>
+      <c r="AC3" s="70"/>
+      <c r="AD3" s="70"/>
+      <c r="AE3" s="70"/>
+      <c r="AF3" s="70"/>
+      <c r="AG3" s="70"/>
+      <c r="AH3" s="70"/>
+      <c r="AI3" s="70"/>
+      <c r="AJ3" s="70"/>
+      <c r="AK3" s="70"/>
+      <c r="AL3" s="70"/>
+      <c r="AM3" s="70"/>
+      <c r="AN3" s="70"/>
+      <c r="AO3" s="70"/>
+      <c r="AP3" s="70"/>
+      <c r="AQ3" s="70"/>
+      <c r="AR3" s="70"/>
+      <c r="AS3" s="70"/>
+      <c r="AT3" s="70"/>
+      <c r="AU3" s="70"/>
+      <c r="AV3" s="70"/>
+      <c r="AW3" s="70"/>
+      <c r="AX3" s="70"/>
+      <c r="AY3" s="70"/>
       <c r="AZ3" s="21"/>
     </row>
     <row r="4" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
@@ -2124,44 +2143,44 @@
       <c r="R4" s="21"/>
       <c r="S4" s="21"/>
       <c r="T4" s="21"/>
-      <c r="V4" s="73" t="s">
+      <c r="V4" s="71" t="s">
         <v>57</v>
       </c>
-      <c r="W4" s="73"/>
-      <c r="X4" s="73"/>
-      <c r="Y4" s="73"/>
-      <c r="Z4" s="73"/>
-      <c r="AA4" s="73"/>
+      <c r="W4" s="71"/>
+      <c r="X4" s="71"/>
+      <c r="Y4" s="71"/>
+      <c r="Z4" s="71"/>
+      <c r="AA4" s="71"/>
       <c r="AB4" s="21"/>
       <c r="AC4" s="21"/>
-      <c r="AD4" s="73" t="s">
+      <c r="AD4" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="AE4" s="73"/>
-      <c r="AF4" s="73"/>
-      <c r="AG4" s="73"/>
+      <c r="AE4" s="71"/>
+      <c r="AF4" s="71"/>
+      <c r="AG4" s="71"/>
       <c r="AH4" s="21"/>
       <c r="AI4" s="21"/>
       <c r="AJ4" s="21"/>
       <c r="AK4" s="21"/>
-      <c r="AL4" s="73" t="s">
+      <c r="AL4" s="71" t="s">
         <v>60</v>
       </c>
-      <c r="AM4" s="73"/>
-      <c r="AN4" s="73"/>
-      <c r="AO4" s="73"/>
-      <c r="AP4" s="73"/>
-      <c r="AQ4" s="73"/>
+      <c r="AM4" s="71"/>
+      <c r="AN4" s="71"/>
+      <c r="AO4" s="71"/>
+      <c r="AP4" s="71"/>
+      <c r="AQ4" s="71"/>
       <c r="AR4" s="21"/>
       <c r="AS4" s="21"/>
-      <c r="AT4" s="73" t="s">
+      <c r="AT4" s="71" t="s">
         <v>61</v>
       </c>
-      <c r="AU4" s="73"/>
-      <c r="AV4" s="73"/>
-      <c r="AW4" s="73"/>
-      <c r="AX4" s="73"/>
-      <c r="AY4" s="73"/>
+      <c r="AU4" s="71"/>
+      <c r="AV4" s="71"/>
+      <c r="AW4" s="71"/>
+      <c r="AX4" s="71"/>
+      <c r="AY4" s="71"/>
       <c r="AZ4" s="21"/>
     </row>
     <row r="5" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
@@ -2303,7 +2322,7 @@
       </c>
     </row>
     <row r="6" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B6" s="70">
+      <c r="B6" s="72">
         <v>0</v>
       </c>
       <c r="C6" s="19">
@@ -2467,7 +2486,7 @@
       </c>
     </row>
     <row r="7" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B7" s="70"/>
+      <c r="B7" s="72"/>
       <c r="C7" s="19">
         <v>1.1000000000000001</v>
       </c>
@@ -2629,7 +2648,7 @@
       </c>
     </row>
     <row r="8" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B8" s="70">
+      <c r="B8" s="72">
         <v>1</v>
       </c>
       <c r="C8" s="18">
@@ -2793,7 +2812,7 @@
       </c>
     </row>
     <row r="9" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="70"/>
+      <c r="B9" s="72"/>
       <c r="C9" s="19">
         <v>1.3</v>
       </c>
@@ -2955,7 +2974,7 @@
       </c>
     </row>
     <row r="10" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B10" s="71">
+      <c r="B10" s="73">
         <v>2</v>
       </c>
       <c r="C10" s="18">
@@ -3119,10 +3138,10 @@
       </c>
     </row>
     <row r="11" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B11" s="71"/>
+      <c r="B11" s="73"/>
     </row>
     <row r="12" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="71"/>
+      <c r="B12" s="73"/>
       <c r="C12" s="19">
         <v>2.1</v>
       </c>
@@ -3284,7 +3303,7 @@
       </c>
     </row>
     <row r="13" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B13" s="70">
+      <c r="B13" s="72">
         <v>3</v>
       </c>
       <c r="C13" s="18">
@@ -3448,7 +3467,7 @@
       </c>
     </row>
     <row r="14" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B14" s="70"/>
+      <c r="B14" s="72"/>
       <c r="C14" s="19">
         <v>2.2999999999999998</v>
       </c>
@@ -3610,7 +3629,7 @@
       </c>
     </row>
     <row r="16" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="70">
+      <c r="B16" s="72">
         <v>4</v>
       </c>
       <c r="C16" s="19">
@@ -3774,7 +3793,7 @@
       </c>
     </row>
     <row r="17" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="70"/>
+      <c r="B17" s="72"/>
       <c r="C17" s="18">
         <v>3.2</v>
       </c>
@@ -3936,7 +3955,7 @@
       </c>
     </row>
     <row r="18" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="70"/>
+      <c r="B18" s="72"/>
       <c r="C18" s="19">
         <v>3.3</v>
       </c>
@@ -4098,7 +4117,7 @@
       </c>
     </row>
     <row r="20" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="70">
+      <c r="B20" s="72">
         <v>5</v>
       </c>
       <c r="C20" s="18">
@@ -4262,7 +4281,7 @@
       </c>
     </row>
     <row r="21" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="70"/>
+      <c r="B21" s="72"/>
       <c r="C21" s="19">
         <v>4.2</v>
       </c>
@@ -4425,18 +4444,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="B16:B18"/>
     <mergeCell ref="D3:P3"/>
     <mergeCell ref="V3:AY3"/>
     <mergeCell ref="AT4:AY4"/>
     <mergeCell ref="AL4:AQ4"/>
     <mergeCell ref="AD4:AG4"/>
     <mergeCell ref="V4:AA4"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B16:B18"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4446,7 +4465,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64F2A8C5-C710-4410-8433-B168C3A556B3}">
-  <dimension ref="A1:U24"/>
+  <dimension ref="A1:U35"/>
   <sheetFormatPr defaultColWidth="16.625" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.625" style="5" customWidth="1"/>
@@ -4463,30 +4482,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E1" s="74" t="s">
+      <c r="E1" s="84" t="s">
         <v>96</v>
       </c>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
+      <c r="F1" s="84"/>
+      <c r="G1" s="84"/>
+      <c r="H1" s="84"/>
       <c r="I1" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="K1" s="75" t="s">
+      <c r="K1" s="85" t="s">
         <v>97</v>
       </c>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="75"/>
+      <c r="L1" s="85"/>
+      <c r="M1" s="85"/>
+      <c r="N1" s="85"/>
       <c r="O1" s="38" t="s">
         <v>159</v>
       </c>
-      <c r="Q1" s="76" t="s">
+      <c r="Q1" s="86" t="s">
         <v>98</v>
       </c>
-      <c r="R1" s="76"/>
-      <c r="S1" s="76"/>
-      <c r="T1" s="76"/>
+      <c r="R1" s="86"/>
+      <c r="S1" s="86"/>
+      <c r="T1" s="86"/>
       <c r="U1" s="39" t="s">
         <v>159</v>
       </c>
@@ -4495,35 +4514,35 @@
       <c r="A2" s="40" t="s">
         <v>158</v>
       </c>
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="87" t="s">
         <v>157</v>
       </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="92" t="s">
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="102" t="s">
         <v>196</v>
       </c>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92" t="s">
+      <c r="F2" s="102"/>
+      <c r="G2" s="102" t="s">
         <v>197</v>
       </c>
-      <c r="H2" s="92"/>
-      <c r="K2" s="92" t="s">
+      <c r="H2" s="102"/>
+      <c r="K2" s="102" t="s">
         <v>196</v>
       </c>
-      <c r="L2" s="92"/>
-      <c r="M2" s="92" t="s">
+      <c r="L2" s="102"/>
+      <c r="M2" s="102" t="s">
         <v>197</v>
       </c>
-      <c r="N2" s="92"/>
-      <c r="Q2" s="92" t="s">
+      <c r="N2" s="102"/>
+      <c r="Q2" s="102" t="s">
         <v>196</v>
       </c>
-      <c r="R2" s="92"/>
-      <c r="S2" s="92" t="s">
+      <c r="R2" s="102"/>
+      <c r="S2" s="102" t="s">
         <v>197</v>
       </c>
-      <c r="T2" s="92"/>
+      <c r="T2" s="102"/>
     </row>
     <row r="3" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="41">
@@ -4536,25 +4555,25 @@
         <v>122</v>
       </c>
       <c r="D3" s="1"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="90" t="s">
+      <c r="E3" s="88"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="90"/>
+      <c r="I3" s="100" t="s">
         <v>129</v>
       </c>
-      <c r="K3" s="78"/>
-      <c r="L3" s="79"/>
-      <c r="M3" s="79"/>
-      <c r="N3" s="80"/>
+      <c r="K3" s="88"/>
+      <c r="L3" s="89"/>
+      <c r="M3" s="89"/>
+      <c r="N3" s="90"/>
       <c r="O3" s="45" t="s">
         <v>129</v>
       </c>
-      <c r="Q3" s="78"/>
-      <c r="R3" s="79"/>
-      <c r="S3" s="79"/>
-      <c r="T3" s="80"/>
-      <c r="U3" s="97" t="s">
+      <c r="Q3" s="88"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="90"/>
+      <c r="U3" s="82" t="s">
         <v>156</v>
       </c>
     </row>
@@ -4567,11 +4586,11 @@
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="81"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="82"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="91"/>
+      <c r="E4" s="91"/>
+      <c r="F4" s="92"/>
+      <c r="G4" s="92"/>
+      <c r="H4" s="93"/>
+      <c r="I4" s="101"/>
       <c r="K4" s="49" t="s">
         <v>133</v>
       </c>
@@ -4580,14 +4599,14 @@
         <v>134</v>
       </c>
       <c r="N4" s="47"/>
-      <c r="O4" s="87">
+      <c r="O4" s="97">
         <v>0</v>
       </c>
-      <c r="Q4" s="84"/>
-      <c r="R4" s="85"/>
-      <c r="S4" s="85"/>
-      <c r="T4" s="86"/>
-      <c r="U4" s="98"/>
+      <c r="Q4" s="94"/>
+      <c r="R4" s="95"/>
+      <c r="S4" s="95"/>
+      <c r="T4" s="96"/>
+      <c r="U4" s="83"/>
     </row>
     <row r="5" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="42">
@@ -4614,7 +4633,7 @@
       <c r="H5" s="48" t="s">
         <v>132</v>
       </c>
-      <c r="I5" s="102">
+      <c r="I5" s="77">
         <v>0</v>
       </c>
       <c r="K5" s="48" t="s">
@@ -4625,12 +4644,12 @@
         <v>194</v>
       </c>
       <c r="N5" s="47"/>
-      <c r="O5" s="88"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="85"/>
-      <c r="S5" s="85"/>
-      <c r="T5" s="86"/>
-      <c r="U5" s="98"/>
+      <c r="O5" s="98"/>
+      <c r="Q5" s="94"/>
+      <c r="R5" s="95"/>
+      <c r="S5" s="95"/>
+      <c r="T5" s="96"/>
+      <c r="U5" s="83"/>
     </row>
     <row r="6" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="42">
@@ -4647,19 +4666,19 @@
         <v>160</v>
       </c>
       <c r="H6" s="47"/>
-      <c r="I6" s="102"/>
+      <c r="I6" s="77"/>
       <c r="K6" s="48" t="s">
         <v>165</v>
       </c>
       <c r="L6" s="48"/>
       <c r="M6" s="48"/>
       <c r="N6" s="47"/>
-      <c r="O6" s="88"/>
-      <c r="Q6" s="81"/>
-      <c r="R6" s="82"/>
-      <c r="S6" s="82"/>
-      <c r="T6" s="83"/>
-      <c r="U6" s="98"/>
+      <c r="O6" s="98"/>
+      <c r="Q6" s="91"/>
+      <c r="R6" s="92"/>
+      <c r="S6" s="92"/>
+      <c r="T6" s="93"/>
+      <c r="U6" s="83"/>
     </row>
     <row r="7" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="42">
@@ -4680,7 +4699,7 @@
         <v>164</v>
       </c>
       <c r="H7" s="47"/>
-      <c r="I7" s="102"/>
+      <c r="I7" s="77"/>
       <c r="K7" s="48" t="s">
         <v>167</v>
       </c>
@@ -4689,7 +4708,7 @@
         <v>166</v>
       </c>
       <c r="N7" s="47"/>
-      <c r="O7" s="89"/>
+      <c r="O7" s="99"/>
       <c r="Q7" s="54" t="s">
         <v>199</v>
       </c>
@@ -4702,7 +4721,7 @@
       <c r="T7" s="51" t="s">
         <v>173</v>
       </c>
-      <c r="U7" s="93">
+      <c r="U7" s="78">
         <v>1</v>
       </c>
     </row>
@@ -4727,7 +4746,7 @@
         <v>169</v>
       </c>
       <c r="H8" s="47"/>
-      <c r="I8" s="102"/>
+      <c r="I8" s="77"/>
       <c r="K8" s="53" t="s">
         <v>136</v>
       </c>
@@ -4740,7 +4759,7 @@
       <c r="N8" s="51" t="s">
         <v>170</v>
       </c>
-      <c r="O8" s="93">
+      <c r="O8" s="78">
         <v>1</v>
       </c>
       <c r="Q8" s="51" t="s">
@@ -4753,7 +4772,7 @@
       <c r="T8" s="51" t="s">
         <v>198</v>
       </c>
-      <c r="U8" s="93"/>
+      <c r="U8" s="78"/>
     </row>
     <row r="9" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="43">
@@ -4778,7 +4797,7 @@
       <c r="H9" s="50" t="s">
         <v>139</v>
       </c>
-      <c r="I9" s="93">
+      <c r="I9" s="78">
         <v>1</v>
       </c>
       <c r="K9" s="51" t="s">
@@ -4793,7 +4812,7 @@
       <c r="N9" s="51" t="s">
         <v>179</v>
       </c>
-      <c r="O9" s="93"/>
+      <c r="O9" s="78"/>
       <c r="Q9" s="33" t="s">
         <v>180</v>
       </c>
@@ -4802,7 +4821,7 @@
         <v>181</v>
       </c>
       <c r="T9" s="56"/>
-      <c r="U9" s="94">
+      <c r="U9" s="79">
         <v>2</v>
       </c>
     </row>
@@ -4821,7 +4840,7 @@
       <c r="F10" s="52"/>
       <c r="G10" s="52"/>
       <c r="H10" s="52"/>
-      <c r="I10" s="93"/>
+      <c r="I10" s="78"/>
       <c r="K10" s="57" t="s">
         <v>141</v>
       </c>
@@ -4832,7 +4851,7 @@
       <c r="N10" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="O10" s="94">
+      <c r="O10" s="79">
         <v>2</v>
       </c>
       <c r="Q10" s="33" t="s">
@@ -4841,7 +4860,7 @@
       <c r="R10" s="56"/>
       <c r="S10" s="56"/>
       <c r="T10" s="56"/>
-      <c r="U10" s="94"/>
+      <c r="U10" s="79"/>
     </row>
     <row r="11" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="65">
@@ -4864,7 +4883,7 @@
       <c r="H11" s="55" t="s">
         <v>145</v>
       </c>
-      <c r="I11" s="94">
+      <c r="I11" s="79">
         <v>2</v>
       </c>
       <c r="K11" s="33"/>
@@ -4873,7 +4892,7 @@
         <v>184</v>
       </c>
       <c r="N11" s="56"/>
-      <c r="O11" s="94"/>
+      <c r="O11" s="79"/>
       <c r="Q11" s="61" t="s">
         <v>183</v>
       </c>
@@ -4882,7 +4901,7 @@
         <v>185</v>
       </c>
       <c r="T11" s="59"/>
-      <c r="U11" s="95">
+      <c r="U11" s="80">
         <v>3</v>
       </c>
     </row>
@@ -4903,21 +4922,21 @@
         <v>186</v>
       </c>
       <c r="H12" s="56"/>
-      <c r="I12" s="94"/>
+      <c r="I12" s="79"/>
       <c r="K12" s="33"/>
       <c r="L12" s="56"/>
       <c r="M12" s="33" t="s">
         <v>187</v>
       </c>
       <c r="N12" s="56"/>
-      <c r="O12" s="94"/>
+      <c r="O12" s="79"/>
       <c r="Q12" s="69" t="s">
         <v>152</v>
       </c>
       <c r="R12" s="59"/>
       <c r="S12" s="59"/>
       <c r="T12" s="59"/>
-      <c r="U12" s="95"/>
+      <c r="U12" s="80"/>
     </row>
     <row r="13" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="65">
@@ -4938,7 +4957,7 @@
       <c r="F13" s="33"/>
       <c r="G13" s="33"/>
       <c r="H13" s="56"/>
-      <c r="I13" s="94"/>
+      <c r="I13" s="79"/>
       <c r="K13" s="60" t="s">
         <v>146</v>
       </c>
@@ -4962,7 +4981,7 @@
       </c>
       <c r="S13" s="63"/>
       <c r="T13" s="63"/>
-      <c r="U13" s="96">
+      <c r="U13" s="81">
         <v>4</v>
       </c>
     </row>
@@ -4983,7 +5002,7 @@
       <c r="F14" s="58"/>
       <c r="G14" s="61"/>
       <c r="H14" s="59"/>
-      <c r="I14" s="95">
+      <c r="I14" s="80">
         <v>3</v>
       </c>
       <c r="K14" s="62"/>
@@ -4992,7 +5011,7 @@
         <v>148</v>
       </c>
       <c r="N14" s="63"/>
-      <c r="O14" s="100">
+      <c r="O14" s="75">
         <v>4</v>
       </c>
       <c r="Q14" s="67" t="s">
@@ -5001,7 +5020,7 @@
       <c r="R14" s="63"/>
       <c r="S14" s="63"/>
       <c r="T14" s="63"/>
-      <c r="U14" s="96"/>
+      <c r="U14" s="81"/>
     </row>
     <row r="15" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="44">
@@ -5018,14 +5037,14 @@
       <c r="F15" s="59"/>
       <c r="G15" s="59"/>
       <c r="H15" s="59"/>
-      <c r="I15" s="95"/>
+      <c r="I15" s="80"/>
       <c r="K15" s="62"/>
       <c r="L15" s="63"/>
       <c r="M15" s="28" t="s">
         <v>151</v>
       </c>
       <c r="N15" s="63"/>
-      <c r="O15" s="101"/>
+      <c r="O15" s="76"/>
       <c r="Q15" s="68" t="s">
         <v>152</v>
       </c>
@@ -5037,10 +5056,10 @@
       </c>
     </row>
     <row r="18" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C18" s="99" t="s">
+      <c r="C18" s="74" t="s">
         <v>99</v>
       </c>
-      <c r="D18" s="99"/>
+      <c r="D18" s="74"/>
     </row>
     <row r="19" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="3" t="s">
@@ -5150,21 +5169,144 @@
         <v>152</v>
       </c>
     </row>
+    <row r="27" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B27" s="5" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B28" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B29" s="5">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5">
+        <v>10</v>
+      </c>
+      <c r="D29" s="5">
+        <v>0</v>
+      </c>
+      <c r="E29" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="F29" s="5">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B30" s="5">
+        <v>1</v>
+      </c>
+      <c r="C30" s="5">
+        <v>20</v>
+      </c>
+      <c r="D30" s="5">
+        <v>10</v>
+      </c>
+      <c r="E30" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="F30" s="5">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B31" s="5">
+        <v>2</v>
+      </c>
+      <c r="C31" s="5">
+        <v>40</v>
+      </c>
+      <c r="D31" s="5">
+        <v>20</v>
+      </c>
+      <c r="E31" s="5">
+        <v>1.4</v>
+      </c>
+      <c r="F31" s="5">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B32" s="5">
+        <v>3</v>
+      </c>
+      <c r="C32" s="5">
+        <v>80</v>
+      </c>
+      <c r="D32" s="5">
+        <v>30</v>
+      </c>
+      <c r="E32" s="5">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F32" s="5">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G32" s="5">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B33" s="5">
+        <v>4</v>
+      </c>
+      <c r="C33" s="5">
+        <v>160</v>
+      </c>
+      <c r="D33" s="5">
+        <v>40</v>
+      </c>
+      <c r="E33" s="114">
+        <v>3.2</v>
+      </c>
+      <c r="F33" s="114">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B34" s="5">
+        <v>5</v>
+      </c>
+      <c r="C34" s="5">
+        <v>320</v>
+      </c>
+      <c r="D34" s="5">
+        <v>50</v>
+      </c>
+      <c r="E34" s="114">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="F34" s="114">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B35" s="5">
+        <v>6</v>
+      </c>
+      <c r="C35" s="5">
+        <v>640</v>
+      </c>
+      <c r="D35" s="5">
+        <v>55</v>
+      </c>
+      <c r="E35" s="114" t="s">
+        <v>152</v>
+      </c>
+      <c r="F35" s="114"/>
+    </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="O14:O15"/>
-    <mergeCell ref="I5:I8"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I11:I13"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="O10:O12"/>
-    <mergeCell ref="U7:U8"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="U11:U12"/>
-    <mergeCell ref="U13:U14"/>
-    <mergeCell ref="U3:U6"/>
     <mergeCell ref="E1:H1"/>
     <mergeCell ref="K1:N1"/>
     <mergeCell ref="Q1:T1"/>
@@ -5180,6 +5322,19 @@
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="K2:L2"/>
+    <mergeCell ref="U7:U8"/>
+    <mergeCell ref="U9:U10"/>
+    <mergeCell ref="U11:U12"/>
+    <mergeCell ref="U13:U14"/>
+    <mergeCell ref="U3:U6"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="O14:O15"/>
+    <mergeCell ref="I5:I8"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I11:I13"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="O10:O12"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5196,32 +5351,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="113" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="G1" s="109" t="s">
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="G1" s="113" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="109"/>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
-      <c r="V1" s="109"/>
-      <c r="W1" s="109"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
+      <c r="V1" s="113"/>
+      <c r="W1" s="113"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
@@ -5394,11 +5549,11 @@
         <f t="shared" ref="E10:E15" si="0">D10*B10</f>
         <v>0.5</v>
       </c>
-      <c r="F10" s="106">
+      <c r="F10" s="109">
         <f>D10+D11+D12+D13</f>
         <v>2</v>
       </c>
-      <c r="G10" s="99">
+      <c r="G10" s="74">
         <v>1.5</v>
       </c>
       <c r="I10" s="1" t="s">
@@ -5418,11 +5573,11 @@
         <f t="shared" ref="M10:M16" si="2">L10*J10</f>
         <v>0.5</v>
       </c>
-      <c r="N10" s="106">
+      <c r="N10" s="109">
         <f>L10+L11+L12+L13+L14+L15+L16</f>
         <v>3.5</v>
       </c>
-      <c r="O10" s="99">
+      <c r="O10" s="74">
         <v>4</v>
       </c>
       <c r="Q10" s="1" t="s">
@@ -5442,7 +5597,7 @@
         <f>T10*R10</f>
         <v>0.5</v>
       </c>
-      <c r="V10" s="110">
+      <c r="V10" s="106">
         <f>T10+T11+T12</f>
         <v>1.84</v>
       </c>
@@ -5465,8 +5620,8 @@
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="F11" s="107"/>
-      <c r="G11" s="99"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="74"/>
       <c r="I11" s="1" t="s">
         <v>19</v>
       </c>
@@ -5484,8 +5639,8 @@
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
-      <c r="N11" s="107"/>
-      <c r="O11" s="99"/>
+      <c r="N11" s="112"/>
+      <c r="O11" s="74"/>
       <c r="Q11" s="1" t="s">
         <v>19</v>
       </c>
@@ -5503,7 +5658,7 @@
         <f>T11*R11</f>
         <v>0.5</v>
       </c>
-      <c r="V11" s="111"/>
+      <c r="V11" s="107"/>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
@@ -5523,8 +5678,8 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F12" s="107"/>
-      <c r="G12" s="99"/>
+      <c r="F12" s="112"/>
+      <c r="G12" s="74"/>
       <c r="I12" s="1" t="s">
         <v>20</v>
       </c>
@@ -5542,8 +5697,8 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="N12" s="107"/>
-      <c r="O12" s="99"/>
+      <c r="N12" s="112"/>
+      <c r="O12" s="74"/>
       <c r="Q12" s="1" t="s">
         <v>21</v>
       </c>
@@ -5561,7 +5716,7 @@
         <f>T12*R12</f>
         <v>1.6800000000000002</v>
       </c>
-      <c r="V12" s="112"/>
+      <c r="V12" s="108"/>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
@@ -5581,8 +5736,8 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F13" s="108"/>
-      <c r="G13" s="99"/>
+      <c r="F13" s="110"/>
+      <c r="G13" s="74"/>
       <c r="I13" s="1" t="s">
         <v>23</v>
       </c>
@@ -5600,8 +5755,8 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="N13" s="107"/>
-      <c r="O13" s="99"/>
+      <c r="N13" s="112"/>
+      <c r="O13" s="74"/>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
@@ -5621,11 +5776,11 @@
         <f t="shared" si="0"/>
         <v>1.575</v>
       </c>
-      <c r="F14" s="106">
+      <c r="F14" s="109">
         <f>D10+D11+D12+D14+D15</f>
         <v>3.09375</v>
       </c>
-      <c r="G14" s="99">
+      <c r="G14" s="74">
         <v>3</v>
       </c>
       <c r="I14" s="1" t="s">
@@ -5645,8 +5800,8 @@
         <f t="shared" si="2"/>
         <v>3.5</v>
       </c>
-      <c r="N14" s="107"/>
-      <c r="O14" s="99"/>
+      <c r="N14" s="112"/>
+      <c r="O14" s="74"/>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
@@ -5666,8 +5821,8 @@
         <f t="shared" si="0"/>
         <v>2.4187500000000002</v>
       </c>
-      <c r="F15" s="108"/>
-      <c r="G15" s="99"/>
+      <c r="F15" s="110"/>
+      <c r="G15" s="74"/>
       <c r="I15" s="1" t="s">
         <v>27</v>
       </c>
@@ -5685,8 +5840,8 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="N15" s="107"/>
-      <c r="O15" s="99"/>
+      <c r="N15" s="112"/>
+      <c r="O15" s="74"/>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.15">
       <c r="D16" s="6" t="s">
@@ -5717,8 +5872,8 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="N16" s="108"/>
-      <c r="O16" s="99"/>
+      <c r="N16" s="110"/>
+      <c r="O16" s="74"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D17" s="6" t="s">
@@ -5854,7 +6009,7 @@
         <f t="shared" ref="M22:M26" si="3">L22*J22</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N22" s="110">
+      <c r="N22" s="106">
         <f>L22+L23+L24</f>
         <v>0.84000000000000008</v>
       </c>
@@ -5894,7 +6049,7 @@
         <f t="shared" si="3"/>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N23" s="111"/>
+      <c r="N23" s="107"/>
       <c r="O23" s="5"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.15">
@@ -5931,7 +6086,7 @@
         <f t="shared" si="3"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="N24" s="112"/>
+      <c r="N24" s="108"/>
       <c r="O24" s="5"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.15">
@@ -5968,7 +6123,7 @@
         <f t="shared" si="3"/>
         <v>0.68</v>
       </c>
-      <c r="N25" s="110">
+      <c r="N25" s="106">
         <f>L22+L23+L25+L26</f>
         <v>1.2400000000000002</v>
       </c>
@@ -5991,7 +6146,7 @@
         <f t="shared" si="3"/>
         <v>0.68</v>
       </c>
-      <c r="N26" s="112"/>
+      <c r="N26" s="108"/>
       <c r="O26" s="5"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.15">
@@ -6005,7 +6160,7 @@
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A30" s="113" t="s">
+      <c r="A30" s="111" t="s">
         <v>43</v>
       </c>
       <c r="B30" s="104"/>
@@ -6014,7 +6169,7 @@
       <c r="E30" s="104"/>
       <c r="F30" s="105"/>
       <c r="G30" s="4"/>
-      <c r="I30" s="113" t="s">
+      <c r="I30" s="111" t="s">
         <v>44</v>
       </c>
       <c r="J30" s="104"/>
@@ -6086,11 +6241,11 @@
         <f t="shared" ref="E32:E37" si="4">D32*B32</f>
         <v>0.70724999999999993</v>
       </c>
-      <c r="F32" s="106">
+      <c r="F32" s="109">
         <f>D32+D33+D34+D35</f>
         <v>2.8634999999999997</v>
       </c>
-      <c r="G32" s="99">
+      <c r="G32" s="74">
         <v>1.5</v>
       </c>
       <c r="I32" s="1" t="s">
@@ -6110,11 +6265,11 @@
         <f t="shared" ref="M32:M38" si="6">L32*J32</f>
         <v>0.70724999999999993</v>
       </c>
-      <c r="N32" s="106">
+      <c r="N32" s="109">
         <f>L32+L33+L34+L35+L36+L37+L38</f>
         <v>4.4731499999999995</v>
       </c>
-      <c r="O32" s="99">
+      <c r="O32" s="74">
         <v>4</v>
       </c>
     </row>
@@ -6136,8 +6291,8 @@
         <f t="shared" si="4"/>
         <v>0.70724999999999993</v>
       </c>
-      <c r="F33" s="107"/>
-      <c r="G33" s="99"/>
+      <c r="F33" s="112"/>
+      <c r="G33" s="74"/>
       <c r="I33" s="1" t="s">
         <v>19</v>
       </c>
@@ -6155,8 +6310,8 @@
         <f t="shared" si="6"/>
         <v>0.70724999999999993</v>
       </c>
-      <c r="N33" s="107"/>
-      <c r="O33" s="99"/>
+      <c r="N33" s="112"/>
+      <c r="O33" s="74"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
@@ -6176,8 +6331,8 @@
         <f t="shared" si="4"/>
         <v>1.4489999999999998</v>
       </c>
-      <c r="F34" s="107"/>
-      <c r="G34" s="99"/>
+      <c r="F34" s="112"/>
+      <c r="G34" s="74"/>
       <c r="I34" s="1" t="s">
         <v>20</v>
       </c>
@@ -6195,8 +6350,8 @@
         <f t="shared" si="6"/>
         <v>1.4489999999999998</v>
       </c>
-      <c r="N34" s="107"/>
-      <c r="O34" s="99"/>
+      <c r="N34" s="112"/>
+      <c r="O34" s="74"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
@@ -6216,8 +6371,8 @@
         <f t="shared" si="4"/>
         <v>1.4489999999999998</v>
       </c>
-      <c r="F35" s="108"/>
-      <c r="G35" s="99"/>
+      <c r="F35" s="110"/>
+      <c r="G35" s="74"/>
       <c r="I35" s="1" t="s">
         <v>23</v>
       </c>
@@ -6235,8 +6390,8 @@
         <f t="shared" si="6"/>
         <v>6.1749999999999989</v>
       </c>
-      <c r="N35" s="107"/>
-      <c r="O35" s="99"/>
+      <c r="N35" s="112"/>
+      <c r="O35" s="74"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
@@ -6256,11 +6411,11 @@
         <f t="shared" si="4"/>
         <v>2.1</v>
       </c>
-      <c r="F36" s="106">
+      <c r="F36" s="109">
         <f>D32+D33+D34+D36+D37</f>
         <v>4.2640000000000002</v>
       </c>
-      <c r="G36" s="99">
+      <c r="G36" s="74">
         <v>3</v>
       </c>
       <c r="I36" s="1" t="s">
@@ -6280,8 +6435,8 @@
         <f t="shared" si="6"/>
         <v>4.0631500000000003</v>
       </c>
-      <c r="N36" s="107"/>
-      <c r="O36" s="99"/>
+      <c r="N36" s="112"/>
+      <c r="O36" s="74"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
@@ -6301,8 +6456,8 @@
         <f t="shared" si="4"/>
         <v>3.2249999999999996</v>
       </c>
-      <c r="F37" s="108"/>
-      <c r="G37" s="99"/>
+      <c r="F37" s="110"/>
+      <c r="G37" s="74"/>
       <c r="I37" s="1" t="s">
         <v>27</v>
       </c>
@@ -6320,8 +6475,8 @@
         <f t="shared" si="6"/>
         <v>6.1749999999999989</v>
       </c>
-      <c r="N37" s="107"/>
-      <c r="O37" s="99"/>
+      <c r="N37" s="112"/>
+      <c r="O37" s="74"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D38" s="6" t="s">
@@ -6352,8 +6507,8 @@
         <f t="shared" si="6"/>
         <v>1.0373999999999999</v>
       </c>
-      <c r="N38" s="108"/>
-      <c r="O38" s="99"/>
+      <c r="N38" s="110"/>
+      <c r="O38" s="74"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D39" s="6" t="s">
@@ -6483,7 +6638,7 @@
         <f t="shared" ref="M45:M49" si="7">L45*J45</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N45" s="110">
+      <c r="N45" s="106">
         <f>L45+L46+L47</f>
         <v>0.84000000000000008</v>
       </c>
@@ -6522,7 +6677,7 @@
         <f t="shared" si="7"/>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N46" s="111"/>
+      <c r="N46" s="107"/>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
@@ -6558,7 +6713,7 @@
         <f t="shared" si="7"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="N47" s="112"/>
+      <c r="N47" s="108"/>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
@@ -6594,7 +6749,7 @@
         <f t="shared" si="7"/>
         <v>0.68</v>
       </c>
-      <c r="N48" s="110">
+      <c r="N48" s="106">
         <f>L45+L46+L48+L49</f>
         <v>1.2400000000000002</v>
       </c>
@@ -6616,29 +6771,10 @@
         <f t="shared" si="7"/>
         <v>0.68</v>
       </c>
-      <c r="N49" s="112"/>
+      <c r="N49" s="108"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="I43:N43"/>
-    <mergeCell ref="N45:N47"/>
-    <mergeCell ref="N48:N49"/>
-    <mergeCell ref="O32:O38"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="I30:N30"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="G32:G35"/>
-    <mergeCell ref="N32:N38"/>
-    <mergeCell ref="N22:N24"/>
-    <mergeCell ref="N25:N26"/>
-    <mergeCell ref="V10:V12"/>
-    <mergeCell ref="G10:G13"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="O10:O16"/>
-    <mergeCell ref="N10:N16"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="I20:N20"/>
     <mergeCell ref="F10:F13"/>
@@ -6648,6 +6784,25 @@
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="I8:N8"/>
     <mergeCell ref="Q8:V8"/>
+    <mergeCell ref="N22:N24"/>
+    <mergeCell ref="N25:N26"/>
+    <mergeCell ref="V10:V12"/>
+    <mergeCell ref="G10:G13"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="O10:O16"/>
+    <mergeCell ref="N10:N16"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="I30:N30"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="G32:G35"/>
+    <mergeCell ref="N32:N38"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="I43:N43"/>
+    <mergeCell ref="N45:N47"/>
+    <mergeCell ref="N48:N49"/>
+    <mergeCell ref="O32:O38"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dev_docs/千界万锻数值表格-26_4_21.xlsx
+++ b/dev_docs/千界万锻数值表格-26_4_21.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\AppData\Roaming\PrismLauncher\instances\SenDimsBanForges\minecraft\dev_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75B67A8F-D0B5-42E0-ACAF-394BBC266FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCAEFACF-BDC6-40E8-AB54-52D350DE6E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-6720" windowWidth="30936" windowHeight="18816" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-6720" windowWidth="30936" windowHeight="18816" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="数值分配" sheetId="3" r:id="rId1"/>
@@ -1583,16 +1583,94 @@
     <xf numFmtId="0" fontId="5" fillId="13" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="8" xfId="8" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1607,81 +1685,6 @@
     <xf numFmtId="0" fontId="0" fillId="25" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="8" xfId="8" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1691,6 +1694,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1700,22 +1715,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2047,57 +2047,57 @@
     </row>
     <row r="3" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C3" s="21"/>
-      <c r="D3" s="70" t="s">
+      <c r="D3" s="73" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
-      <c r="I3" s="70"/>
-      <c r="J3" s="70"/>
-      <c r="K3" s="70"/>
-      <c r="L3" s="70"/>
-      <c r="M3" s="70"/>
-      <c r="N3" s="70"/>
-      <c r="O3" s="70"/>
-      <c r="P3" s="70"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
+      <c r="K3" s="73"/>
+      <c r="L3" s="73"/>
+      <c r="M3" s="73"/>
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
       <c r="Q3" s="21"/>
       <c r="R3" s="21"/>
       <c r="S3" s="21"/>
       <c r="T3" s="21"/>
-      <c r="V3" s="70" t="s">
+      <c r="V3" s="73" t="s">
         <v>52</v>
       </c>
-      <c r="W3" s="70"/>
-      <c r="X3" s="70"/>
-      <c r="Y3" s="70"/>
-      <c r="Z3" s="70"/>
-      <c r="AA3" s="70"/>
-      <c r="AB3" s="70"/>
-      <c r="AC3" s="70"/>
-      <c r="AD3" s="70"/>
-      <c r="AE3" s="70"/>
-      <c r="AF3" s="70"/>
-      <c r="AG3" s="70"/>
-      <c r="AH3" s="70"/>
-      <c r="AI3" s="70"/>
-      <c r="AJ3" s="70"/>
-      <c r="AK3" s="70"/>
-      <c r="AL3" s="70"/>
-      <c r="AM3" s="70"/>
-      <c r="AN3" s="70"/>
-      <c r="AO3" s="70"/>
-      <c r="AP3" s="70"/>
-      <c r="AQ3" s="70"/>
-      <c r="AR3" s="70"/>
-      <c r="AS3" s="70"/>
-      <c r="AT3" s="70"/>
-      <c r="AU3" s="70"/>
-      <c r="AV3" s="70"/>
-      <c r="AW3" s="70"/>
-      <c r="AX3" s="70"/>
-      <c r="AY3" s="70"/>
+      <c r="W3" s="73"/>
+      <c r="X3" s="73"/>
+      <c r="Y3" s="73"/>
+      <c r="Z3" s="73"/>
+      <c r="AA3" s="73"/>
+      <c r="AB3" s="73"/>
+      <c r="AC3" s="73"/>
+      <c r="AD3" s="73"/>
+      <c r="AE3" s="73"/>
+      <c r="AF3" s="73"/>
+      <c r="AG3" s="73"/>
+      <c r="AH3" s="73"/>
+      <c r="AI3" s="73"/>
+      <c r="AJ3" s="73"/>
+      <c r="AK3" s="73"/>
+      <c r="AL3" s="73"/>
+      <c r="AM3" s="73"/>
+      <c r="AN3" s="73"/>
+      <c r="AO3" s="73"/>
+      <c r="AP3" s="73"/>
+      <c r="AQ3" s="73"/>
+      <c r="AR3" s="73"/>
+      <c r="AS3" s="73"/>
+      <c r="AT3" s="73"/>
+      <c r="AU3" s="73"/>
+      <c r="AV3" s="73"/>
+      <c r="AW3" s="73"/>
+      <c r="AX3" s="73"/>
+      <c r="AY3" s="73"/>
       <c r="AZ3" s="21"/>
     </row>
     <row r="4" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
@@ -2143,44 +2143,44 @@
       <c r="R4" s="21"/>
       <c r="S4" s="21"/>
       <c r="T4" s="21"/>
-      <c r="V4" s="71" t="s">
+      <c r="V4" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="W4" s="71"/>
-      <c r="X4" s="71"/>
-      <c r="Y4" s="71"/>
-      <c r="Z4" s="71"/>
-      <c r="AA4" s="71"/>
+      <c r="W4" s="74"/>
+      <c r="X4" s="74"/>
+      <c r="Y4" s="74"/>
+      <c r="Z4" s="74"/>
+      <c r="AA4" s="74"/>
       <c r="AB4" s="21"/>
       <c r="AC4" s="21"/>
-      <c r="AD4" s="71" t="s">
+      <c r="AD4" s="74" t="s">
         <v>59</v>
       </c>
-      <c r="AE4" s="71"/>
-      <c r="AF4" s="71"/>
-      <c r="AG4" s="71"/>
+      <c r="AE4" s="74"/>
+      <c r="AF4" s="74"/>
+      <c r="AG4" s="74"/>
       <c r="AH4" s="21"/>
       <c r="AI4" s="21"/>
       <c r="AJ4" s="21"/>
       <c r="AK4" s="21"/>
-      <c r="AL4" s="71" t="s">
+      <c r="AL4" s="74" t="s">
         <v>60</v>
       </c>
-      <c r="AM4" s="71"/>
-      <c r="AN4" s="71"/>
-      <c r="AO4" s="71"/>
-      <c r="AP4" s="71"/>
-      <c r="AQ4" s="71"/>
+      <c r="AM4" s="74"/>
+      <c r="AN4" s="74"/>
+      <c r="AO4" s="74"/>
+      <c r="AP4" s="74"/>
+      <c r="AQ4" s="74"/>
       <c r="AR4" s="21"/>
       <c r="AS4" s="21"/>
-      <c r="AT4" s="71" t="s">
+      <c r="AT4" s="74" t="s">
         <v>61</v>
       </c>
-      <c r="AU4" s="71"/>
-      <c r="AV4" s="71"/>
-      <c r="AW4" s="71"/>
-      <c r="AX4" s="71"/>
-      <c r="AY4" s="71"/>
+      <c r="AU4" s="74"/>
+      <c r="AV4" s="74"/>
+      <c r="AW4" s="74"/>
+      <c r="AX4" s="74"/>
+      <c r="AY4" s="74"/>
       <c r="AZ4" s="21"/>
     </row>
     <row r="5" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
@@ -2322,7 +2322,7 @@
       </c>
     </row>
     <row r="6" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B6" s="72">
+      <c r="B6" s="71">
         <v>0</v>
       </c>
       <c r="C6" s="19">
@@ -2371,25 +2371,25 @@
       </c>
       <c r="Q6" s="22">
         <f>(V6-MAX($D$2,P6))*N6</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R6" s="22">
         <f>K6/Q6</f>
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S6" s="22">
         <f>(AD6-MAX($D$2,P6))*N6</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T6" s="22">
         <f>K6/S6</f>
-        <v>5.5</v>
+        <v>22</v>
       </c>
       <c r="U6" s="8">
         <v>0</v>
       </c>
       <c r="V6" s="12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W6" s="15">
         <v>20</v>
@@ -2413,7 +2413,7 @@
         <v>1.1933060304913559</v>
       </c>
       <c r="AD6" s="12">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE6" s="15">
         <v>18</v>
@@ -2486,7 +2486,7 @@
       </c>
     </row>
     <row r="7" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B7" s="72"/>
+      <c r="B7" s="71"/>
       <c r="C7" s="19">
         <v>1.1000000000000001</v>
       </c>
@@ -2533,25 +2533,25 @@
       </c>
       <c r="Q7" s="22">
         <f>(V7-MAX($D$2,P7))*N7</f>
-        <v>3.6799999999999997</v>
+        <v>1.6799999999999997</v>
       </c>
       <c r="R7" s="22">
         <f>K7/Q7</f>
-        <v>10.869565217391305</v>
+        <v>23.809523809523814</v>
       </c>
       <c r="S7" s="22">
         <f>(AD7-MAX($D$2,P7))*N7</f>
-        <v>7.68</v>
+        <v>3.6799999999999997</v>
       </c>
       <c r="T7" s="22">
         <f>K7/S7</f>
-        <v>5.2083333333333339</v>
+        <v>10.869565217391305</v>
       </c>
       <c r="U7" s="7" t="s">
         <v>93</v>
       </c>
       <c r="V7" s="12">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="W7" s="15">
         <v>55</v>
@@ -2575,7 +2575,7 @@
         <v>1.1187413338228132</v>
       </c>
       <c r="AD7" s="12">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE7" s="15">
         <v>35</v>
@@ -2648,7 +2648,7 @@
       </c>
     </row>
     <row r="8" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B8" s="72">
+      <c r="B8" s="71">
         <v>1</v>
       </c>
       <c r="C8" s="18">
@@ -2697,25 +2697,25 @@
       </c>
       <c r="Q8" s="22">
         <f>(V8-MAX($D$2,P8))*N8</f>
-        <v>9.5379999999999985</v>
+        <v>7.637999999999999</v>
       </c>
       <c r="R8" s="22">
         <f>K8/Q8</f>
-        <v>10.484378276368213</v>
+        <v>13.092432573972246</v>
       </c>
       <c r="S8" s="22">
         <f>(AD8-MAX($D$2,P8))*N8</f>
-        <v>18.087999999999997</v>
+        <v>11.437999999999999</v>
       </c>
       <c r="T8" s="22">
         <f>K8/S8</f>
-        <v>5.5285272003538264</v>
+        <v>8.7427872005595386</v>
       </c>
       <c r="U8" s="8">
         <v>1</v>
       </c>
       <c r="V8" s="12">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="W8" s="15">
         <v>110</v>
@@ -2739,7 +2739,7 @@
         <v>1.1988870840188786</v>
       </c>
       <c r="AD8" s="12">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AE8" s="15">
         <v>64</v>
@@ -2812,7 +2812,7 @@
       </c>
     </row>
     <row r="9" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="72"/>
+      <c r="B9" s="71"/>
       <c r="C9" s="19">
         <v>1.3</v>
       </c>
@@ -2867,11 +2867,11 @@
       </c>
       <c r="S9" s="22">
         <f>(AD9-MAX($D$2,P9))*N9</f>
-        <v>38.075999999999993</v>
+        <v>28.575999999999997</v>
       </c>
       <c r="T9" s="22">
         <f>K9/S9</f>
-        <v>5.2526525895577274</v>
+        <v>6.9988801791713335</v>
       </c>
       <c r="U9" s="36" t="s">
         <v>92</v>
@@ -2901,7 +2901,7 @@
         <v>1.2087705629140901</v>
       </c>
       <c r="AD9" s="12">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="AE9" s="15">
         <v>115</v>
@@ -2974,7 +2974,7 @@
       </c>
     </row>
     <row r="10" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B10" s="73">
+      <c r="B10" s="72">
         <v>2</v>
       </c>
       <c r="C10" s="18">
@@ -3031,11 +3031,11 @@
       </c>
       <c r="S10" s="22">
         <f>(AD10-MAX($D$2,P10))*N10</f>
-        <v>64.62</v>
+        <v>46.62</v>
       </c>
       <c r="T10" s="22">
         <f>K10/S10</f>
-        <v>5.2615289384091612</v>
+        <v>7.2930072930072933</v>
       </c>
       <c r="U10" s="7" t="s">
         <v>92</v>
@@ -3065,7 +3065,7 @@
         <v>1.2183932544550955</v>
       </c>
       <c r="AD10" s="12">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AE10" s="15">
         <v>225</v>
@@ -3138,10 +3138,10 @@
       </c>
     </row>
     <row r="11" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B11" s="73"/>
+      <c r="B11" s="72"/>
     </row>
     <row r="12" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="73"/>
+      <c r="B12" s="72"/>
       <c r="C12" s="19">
         <v>2.1</v>
       </c>
@@ -3196,11 +3196,11 @@
       </c>
       <c r="S12" s="22">
         <f>(AD12-MAX($D$2,P12))*N12</f>
-        <v>100.8</v>
+        <v>78.3</v>
       </c>
       <c r="T12" s="22">
         <f>K12/S12</f>
-        <v>5.3571428571428577</v>
+        <v>6.8965517241379315</v>
       </c>
       <c r="U12" s="7" t="s">
         <v>92</v>
@@ -3230,7 +3230,7 @@
         <v>1.2276179669255169</v>
       </c>
       <c r="AD12" s="12">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="AE12" s="33">
         <v>380</v>
@@ -3303,7 +3303,7 @@
       </c>
     </row>
     <row r="13" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B13" s="72">
+      <c r="B13" s="71">
         <v>3</v>
       </c>
       <c r="C13" s="18">
@@ -3360,11 +3360,11 @@
       </c>
       <c r="S13" s="22">
         <f>(AD13-MAX($D$2,P13))*N13</f>
-        <v>138.72</v>
+        <v>108.96999999999998</v>
       </c>
       <c r="T13" s="22">
         <f>K13/S13</f>
-        <v>5.3344867358708186</v>
+        <v>6.790859869688906</v>
       </c>
       <c r="U13" s="8">
         <v>2</v>
@@ -3394,7 +3394,7 @@
         <v>1.2565491340868609</v>
       </c>
       <c r="AD13" s="12">
-        <v>240</v>
+        <v>205</v>
       </c>
       <c r="AE13" s="15">
         <v>650</v>
@@ -3467,7 +3467,7 @@
       </c>
     </row>
     <row r="14" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B14" s="72"/>
+      <c r="B14" s="71"/>
       <c r="C14" s="19">
         <v>2.2999999999999998</v>
       </c>
@@ -3522,11 +3522,11 @@
       </c>
       <c r="S14" s="22">
         <f>(AD14-MAX($D$2,P14))*N14</f>
-        <v>188.02</v>
+        <v>145.52000000000001</v>
       </c>
       <c r="T14" s="22">
         <f>K14/S14</f>
-        <v>5.3185831294543133</v>
+        <v>6.8719076415612967</v>
       </c>
       <c r="U14" s="7" t="s">
         <v>94</v>
@@ -3556,7 +3556,7 @@
         <v>1.2981485969928603</v>
       </c>
       <c r="AD14" s="12">
-        <v>330</v>
+        <v>280</v>
       </c>
       <c r="AE14" s="15">
         <v>1100</v>
@@ -3629,7 +3629,7 @@
       </c>
     </row>
     <row r="16" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="72">
+      <c r="B16" s="71">
         <v>4</v>
       </c>
       <c r="C16" s="19">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="S16" s="22">
         <f>(AD16-MAX($D$2,P16))*N16</f>
-        <v>266.24</v>
+        <v>206.24</v>
       </c>
       <c r="T16" s="22">
         <f>K16/S16</f>
-        <v>4.8828125</v>
+        <v>6.3033359193173002</v>
       </c>
       <c r="U16" s="8">
         <v>3</v>
@@ -3720,7 +3720,7 @@
         <v>1.29414385593481</v>
       </c>
       <c r="AD16" s="12">
-        <v>500</v>
+        <v>425</v>
       </c>
       <c r="AE16" s="15">
         <v>1700</v>
@@ -3793,7 +3793,7 @@
       </c>
     </row>
     <row r="17" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="72"/>
+      <c r="B17" s="71"/>
       <c r="C17" s="18">
         <v>3.2</v>
       </c>
@@ -3848,11 +3848,11 @@
       </c>
       <c r="S17" s="22">
         <f>(AD17-MAX($D$2,P17))*N17</f>
-        <v>331.84</v>
+        <v>291.83999999999997</v>
       </c>
       <c r="T17" s="22">
         <f>K17/S17</f>
-        <v>4.821600771456124</v>
+        <v>5.4824561403508776</v>
       </c>
       <c r="U17" s="7" t="s">
         <v>95</v>
@@ -3882,7 +3882,7 @@
         <v>1.3107754920878065</v>
       </c>
       <c r="AD17" s="12">
-        <v>650</v>
+        <v>600</v>
       </c>
       <c r="AE17" s="15">
         <v>2500</v>
@@ -3955,7 +3955,7 @@
       </c>
     </row>
     <row r="18" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="72"/>
+      <c r="B18" s="71"/>
       <c r="C18" s="19">
         <v>3.3</v>
       </c>
@@ -4010,11 +4010,11 @@
       </c>
       <c r="S18" s="22">
         <f>(AD18-MAX($D$2,P18))*N18</f>
-        <v>411.04</v>
+        <v>341.04</v>
       </c>
       <c r="T18" s="22">
         <f>K18/S18</f>
-        <v>4.62242117555469</v>
+        <v>5.571193994839315</v>
       </c>
       <c r="U18" s="7" t="s">
         <v>95</v>
@@ -4044,7 +4044,7 @@
         <v>1.3135419902595107</v>
       </c>
       <c r="AD18" s="12">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="AE18" s="15">
         <v>3600</v>
@@ -4117,7 +4117,7 @@
       </c>
     </row>
     <row r="20" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="72">
+      <c r="B20" s="71">
         <v>5</v>
       </c>
       <c r="C20" s="18">
@@ -4174,11 +4174,11 @@
       </c>
       <c r="S20" s="22">
         <f>(AD20-MAX($D$2,P20))*N20</f>
-        <v>501.53999999999996</v>
+        <v>436.53999999999996</v>
       </c>
       <c r="T20" s="22">
         <f>K20/S20</f>
-        <v>4.0275950073772782</v>
+        <v>4.6272964676776471</v>
       </c>
       <c r="U20" s="8">
         <v>4</v>
@@ -4208,7 +4208,7 @@
         <v>1.3996480584956914</v>
       </c>
       <c r="AD20" s="12">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="AE20" s="15">
         <v>7000</v>
@@ -4281,7 +4281,7 @@
       </c>
     </row>
     <row r="21" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="72"/>
+      <c r="B21" s="71"/>
       <c r="C21" s="19">
         <v>4.2</v>
       </c>
@@ -4336,11 +4336,11 @@
       </c>
       <c r="S21" s="22">
         <f>(AD21-MAX($D$2,P21))*N21</f>
-        <v>738</v>
+        <v>678</v>
       </c>
       <c r="T21" s="22">
         <f>K21/S21</f>
-        <v>3.9295392953929538</v>
+        <v>4.277286135693215</v>
       </c>
       <c r="U21" s="8">
         <v>5</v>
@@ -4370,7 +4370,7 @@
         <v>1.3866757543848907</v>
       </c>
       <c r="AD21" s="12">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="AE21" s="15">
         <v>11000</v>
@@ -4444,18 +4444,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="D3:P3"/>
+    <mergeCell ref="V3:AY3"/>
+    <mergeCell ref="AT4:AY4"/>
+    <mergeCell ref="AL4:AQ4"/>
+    <mergeCell ref="AD4:AG4"/>
+    <mergeCell ref="V4:AA4"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="B10:B12"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="B16:B18"/>
-    <mergeCell ref="D3:P3"/>
-    <mergeCell ref="V3:AY3"/>
-    <mergeCell ref="AT4:AY4"/>
-    <mergeCell ref="AL4:AQ4"/>
-    <mergeCell ref="AD4:AG4"/>
-    <mergeCell ref="V4:AA4"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4482,30 +4482,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E1" s="84" t="s">
+      <c r="E1" s="75" t="s">
         <v>96</v>
       </c>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
       <c r="I1" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="K1" s="85" t="s">
+      <c r="K1" s="76" t="s">
         <v>97</v>
       </c>
-      <c r="L1" s="85"/>
-      <c r="M1" s="85"/>
-      <c r="N1" s="85"/>
+      <c r="L1" s="76"/>
+      <c r="M1" s="76"/>
+      <c r="N1" s="76"/>
       <c r="O1" s="38" t="s">
         <v>159</v>
       </c>
-      <c r="Q1" s="86" t="s">
+      <c r="Q1" s="77" t="s">
         <v>98</v>
       </c>
-      <c r="R1" s="86"/>
-      <c r="S1" s="86"/>
-      <c r="T1" s="86"/>
+      <c r="R1" s="77"/>
+      <c r="S1" s="77"/>
+      <c r="T1" s="77"/>
       <c r="U1" s="39" t="s">
         <v>159</v>
       </c>
@@ -4514,35 +4514,35 @@
       <c r="A2" s="40" t="s">
         <v>158</v>
       </c>
-      <c r="B2" s="87" t="s">
+      <c r="B2" s="78" t="s">
         <v>157</v>
       </c>
-      <c r="C2" s="87"/>
-      <c r="D2" s="87"/>
-      <c r="E2" s="102" t="s">
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="93" t="s">
         <v>196</v>
       </c>
-      <c r="F2" s="102"/>
-      <c r="G2" s="102" t="s">
+      <c r="F2" s="93"/>
+      <c r="G2" s="93" t="s">
         <v>197</v>
       </c>
-      <c r="H2" s="102"/>
-      <c r="K2" s="102" t="s">
+      <c r="H2" s="93"/>
+      <c r="K2" s="93" t="s">
         <v>196</v>
       </c>
-      <c r="L2" s="102"/>
-      <c r="M2" s="102" t="s">
+      <c r="L2" s="93"/>
+      <c r="M2" s="93" t="s">
         <v>197</v>
       </c>
-      <c r="N2" s="102"/>
-      <c r="Q2" s="102" t="s">
+      <c r="N2" s="93"/>
+      <c r="Q2" s="93" t="s">
         <v>196</v>
       </c>
-      <c r="R2" s="102"/>
-      <c r="S2" s="102" t="s">
+      <c r="R2" s="93"/>
+      <c r="S2" s="93" t="s">
         <v>197</v>
       </c>
-      <c r="T2" s="102"/>
+      <c r="T2" s="93"/>
     </row>
     <row r="3" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="41">
@@ -4555,25 +4555,25 @@
         <v>122</v>
       </c>
       <c r="D3" s="1"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="90"/>
-      <c r="I3" s="100" t="s">
+      <c r="E3" s="79"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="91" t="s">
         <v>129</v>
       </c>
-      <c r="K3" s="88"/>
-      <c r="L3" s="89"/>
-      <c r="M3" s="89"/>
-      <c r="N3" s="90"/>
+      <c r="K3" s="79"/>
+      <c r="L3" s="80"/>
+      <c r="M3" s="80"/>
+      <c r="N3" s="81"/>
       <c r="O3" s="45" t="s">
         <v>129</v>
       </c>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="89"/>
-      <c r="S3" s="89"/>
-      <c r="T3" s="90"/>
-      <c r="U3" s="82" t="s">
+      <c r="Q3" s="79"/>
+      <c r="R3" s="80"/>
+      <c r="S3" s="80"/>
+      <c r="T3" s="81"/>
+      <c r="U3" s="98" t="s">
         <v>156</v>
       </c>
     </row>
@@ -4586,11 +4586,11 @@
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="91"/>
-      <c r="F4" s="92"/>
-      <c r="G4" s="92"/>
-      <c r="H4" s="93"/>
-      <c r="I4" s="101"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="83"/>
+      <c r="H4" s="84"/>
+      <c r="I4" s="92"/>
       <c r="K4" s="49" t="s">
         <v>133</v>
       </c>
@@ -4599,14 +4599,14 @@
         <v>134</v>
       </c>
       <c r="N4" s="47"/>
-      <c r="O4" s="97">
+      <c r="O4" s="88">
         <v>0</v>
       </c>
-      <c r="Q4" s="94"/>
-      <c r="R4" s="95"/>
-      <c r="S4" s="95"/>
-      <c r="T4" s="96"/>
-      <c r="U4" s="83"/>
+      <c r="Q4" s="85"/>
+      <c r="R4" s="86"/>
+      <c r="S4" s="86"/>
+      <c r="T4" s="87"/>
+      <c r="U4" s="99"/>
     </row>
     <row r="5" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="42">
@@ -4633,7 +4633,7 @@
       <c r="H5" s="48" t="s">
         <v>132</v>
       </c>
-      <c r="I5" s="77">
+      <c r="I5" s="103">
         <v>0</v>
       </c>
       <c r="K5" s="48" t="s">
@@ -4644,12 +4644,12 @@
         <v>194</v>
       </c>
       <c r="N5" s="47"/>
-      <c r="O5" s="98"/>
-      <c r="Q5" s="94"/>
-      <c r="R5" s="95"/>
-      <c r="S5" s="95"/>
-      <c r="T5" s="96"/>
-      <c r="U5" s="83"/>
+      <c r="O5" s="89"/>
+      <c r="Q5" s="85"/>
+      <c r="R5" s="86"/>
+      <c r="S5" s="86"/>
+      <c r="T5" s="87"/>
+      <c r="U5" s="99"/>
     </row>
     <row r="6" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="42">
@@ -4666,19 +4666,19 @@
         <v>160</v>
       </c>
       <c r="H6" s="47"/>
-      <c r="I6" s="77"/>
+      <c r="I6" s="103"/>
       <c r="K6" s="48" t="s">
         <v>165</v>
       </c>
       <c r="L6" s="48"/>
       <c r="M6" s="48"/>
       <c r="N6" s="47"/>
-      <c r="O6" s="98"/>
-      <c r="Q6" s="91"/>
-      <c r="R6" s="92"/>
-      <c r="S6" s="92"/>
-      <c r="T6" s="93"/>
-      <c r="U6" s="83"/>
+      <c r="O6" s="89"/>
+      <c r="Q6" s="82"/>
+      <c r="R6" s="83"/>
+      <c r="S6" s="83"/>
+      <c r="T6" s="84"/>
+      <c r="U6" s="99"/>
     </row>
     <row r="7" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="42">
@@ -4699,7 +4699,7 @@
         <v>164</v>
       </c>
       <c r="H7" s="47"/>
-      <c r="I7" s="77"/>
+      <c r="I7" s="103"/>
       <c r="K7" s="48" t="s">
         <v>167</v>
       </c>
@@ -4708,7 +4708,7 @@
         <v>166</v>
       </c>
       <c r="N7" s="47"/>
-      <c r="O7" s="99"/>
+      <c r="O7" s="90"/>
       <c r="Q7" s="54" t="s">
         <v>199</v>
       </c>
@@ -4721,7 +4721,7 @@
       <c r="T7" s="51" t="s">
         <v>173</v>
       </c>
-      <c r="U7" s="78">
+      <c r="U7" s="94">
         <v>1</v>
       </c>
     </row>
@@ -4746,7 +4746,7 @@
         <v>169</v>
       </c>
       <c r="H8" s="47"/>
-      <c r="I8" s="77"/>
+      <c r="I8" s="103"/>
       <c r="K8" s="53" t="s">
         <v>136</v>
       </c>
@@ -4759,7 +4759,7 @@
       <c r="N8" s="51" t="s">
         <v>170</v>
       </c>
-      <c r="O8" s="78">
+      <c r="O8" s="94">
         <v>1</v>
       </c>
       <c r="Q8" s="51" t="s">
@@ -4772,7 +4772,7 @@
       <c r="T8" s="51" t="s">
         <v>198</v>
       </c>
-      <c r="U8" s="78"/>
+      <c r="U8" s="94"/>
     </row>
     <row r="9" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="43">
@@ -4797,7 +4797,7 @@
       <c r="H9" s="50" t="s">
         <v>139</v>
       </c>
-      <c r="I9" s="78">
+      <c r="I9" s="94">
         <v>1</v>
       </c>
       <c r="K9" s="51" t="s">
@@ -4812,7 +4812,7 @@
       <c r="N9" s="51" t="s">
         <v>179</v>
       </c>
-      <c r="O9" s="78"/>
+      <c r="O9" s="94"/>
       <c r="Q9" s="33" t="s">
         <v>180</v>
       </c>
@@ -4821,7 +4821,7 @@
         <v>181</v>
       </c>
       <c r="T9" s="56"/>
-      <c r="U9" s="79">
+      <c r="U9" s="95">
         <v>2</v>
       </c>
     </row>
@@ -4840,7 +4840,7 @@
       <c r="F10" s="52"/>
       <c r="G10" s="52"/>
       <c r="H10" s="52"/>
-      <c r="I10" s="78"/>
+      <c r="I10" s="94"/>
       <c r="K10" s="57" t="s">
         <v>141</v>
       </c>
@@ -4851,7 +4851,7 @@
       <c r="N10" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="O10" s="79">
+      <c r="O10" s="95">
         <v>2</v>
       </c>
       <c r="Q10" s="33" t="s">
@@ -4860,7 +4860,7 @@
       <c r="R10" s="56"/>
       <c r="S10" s="56"/>
       <c r="T10" s="56"/>
-      <c r="U10" s="79"/>
+      <c r="U10" s="95"/>
     </row>
     <row r="11" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="65">
@@ -4883,7 +4883,7 @@
       <c r="H11" s="55" t="s">
         <v>145</v>
       </c>
-      <c r="I11" s="79">
+      <c r="I11" s="95">
         <v>2</v>
       </c>
       <c r="K11" s="33"/>
@@ -4892,7 +4892,7 @@
         <v>184</v>
       </c>
       <c r="N11" s="56"/>
-      <c r="O11" s="79"/>
+      <c r="O11" s="95"/>
       <c r="Q11" s="61" t="s">
         <v>183</v>
       </c>
@@ -4901,7 +4901,7 @@
         <v>185</v>
       </c>
       <c r="T11" s="59"/>
-      <c r="U11" s="80">
+      <c r="U11" s="96">
         <v>3</v>
       </c>
     </row>
@@ -4922,21 +4922,21 @@
         <v>186</v>
       </c>
       <c r="H12" s="56"/>
-      <c r="I12" s="79"/>
+      <c r="I12" s="95"/>
       <c r="K12" s="33"/>
       <c r="L12" s="56"/>
       <c r="M12" s="33" t="s">
         <v>187</v>
       </c>
       <c r="N12" s="56"/>
-      <c r="O12" s="79"/>
+      <c r="O12" s="95"/>
       <c r="Q12" s="69" t="s">
         <v>152</v>
       </c>
       <c r="R12" s="59"/>
       <c r="S12" s="59"/>
       <c r="T12" s="59"/>
-      <c r="U12" s="80"/>
+      <c r="U12" s="96"/>
     </row>
     <row r="13" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="65">
@@ -4957,7 +4957,7 @@
       <c r="F13" s="33"/>
       <c r="G13" s="33"/>
       <c r="H13" s="56"/>
-      <c r="I13" s="79"/>
+      <c r="I13" s="95"/>
       <c r="K13" s="60" t="s">
         <v>146</v>
       </c>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="S13" s="63"/>
       <c r="T13" s="63"/>
-      <c r="U13" s="81">
+      <c r="U13" s="97">
         <v>4</v>
       </c>
     </row>
@@ -5002,7 +5002,7 @@
       <c r="F14" s="58"/>
       <c r="G14" s="61"/>
       <c r="H14" s="59"/>
-      <c r="I14" s="80">
+      <c r="I14" s="96">
         <v>3</v>
       </c>
       <c r="K14" s="62"/>
@@ -5011,7 +5011,7 @@
         <v>148</v>
       </c>
       <c r="N14" s="63"/>
-      <c r="O14" s="75">
+      <c r="O14" s="101">
         <v>4</v>
       </c>
       <c r="Q14" s="67" t="s">
@@ -5020,7 +5020,7 @@
       <c r="R14" s="63"/>
       <c r="S14" s="63"/>
       <c r="T14" s="63"/>
-      <c r="U14" s="81"/>
+      <c r="U14" s="97"/>
     </row>
     <row r="15" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="44">
@@ -5037,14 +5037,14 @@
       <c r="F15" s="59"/>
       <c r="G15" s="59"/>
       <c r="H15" s="59"/>
-      <c r="I15" s="80"/>
+      <c r="I15" s="96"/>
       <c r="K15" s="62"/>
       <c r="L15" s="63"/>
       <c r="M15" s="28" t="s">
         <v>151</v>
       </c>
       <c r="N15" s="63"/>
-      <c r="O15" s="76"/>
+      <c r="O15" s="102"/>
       <c r="Q15" s="68" t="s">
         <v>152</v>
       </c>
@@ -5056,10 +5056,10 @@
       </c>
     </row>
     <row r="18" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C18" s="74" t="s">
+      <c r="C18" s="100" t="s">
         <v>99</v>
       </c>
-      <c r="D18" s="74"/>
+      <c r="D18" s="100"/>
     </row>
     <row r="19" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="3" t="s">
@@ -5266,10 +5266,10 @@
       <c r="D33" s="5">
         <v>40</v>
       </c>
-      <c r="E33" s="114">
+      <c r="E33" s="70">
         <v>3.2</v>
       </c>
-      <c r="F33" s="114">
+      <c r="F33" s="70">
         <v>3.3</v>
       </c>
     </row>
@@ -5283,10 +5283,10 @@
       <c r="D34" s="5">
         <v>50</v>
       </c>
-      <c r="E34" s="114">
+      <c r="E34" s="70">
         <v>4.0999999999999996</v>
       </c>
-      <c r="F34" s="114">
+      <c r="F34" s="70">
         <v>4.2</v>
       </c>
     </row>
@@ -5300,13 +5300,26 @@
       <c r="D35" s="5">
         <v>55</v>
       </c>
-      <c r="E35" s="114" t="s">
+      <c r="E35" s="70" t="s">
         <v>152</v>
       </c>
-      <c r="F35" s="114"/>
+      <c r="F35" s="70"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="O14:O15"/>
+    <mergeCell ref="I5:I8"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I11:I13"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="O10:O12"/>
+    <mergeCell ref="U7:U8"/>
+    <mergeCell ref="U9:U10"/>
+    <mergeCell ref="U11:U12"/>
+    <mergeCell ref="U13:U14"/>
+    <mergeCell ref="U3:U6"/>
     <mergeCell ref="E1:H1"/>
     <mergeCell ref="K1:N1"/>
     <mergeCell ref="Q1:T1"/>
@@ -5322,19 +5335,6 @@
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="K2:L2"/>
-    <mergeCell ref="U7:U8"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="U11:U12"/>
-    <mergeCell ref="U13:U14"/>
-    <mergeCell ref="U3:U6"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="O14:O15"/>
-    <mergeCell ref="I5:I8"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I11:I13"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="O10:O12"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5351,32 +5351,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="110" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="113"/>
-      <c r="C1" s="113"/>
-      <c r="D1" s="113"/>
-      <c r="E1" s="113"/>
-      <c r="G1" s="113" t="s">
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="G1" s="110" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="113"/>
-      <c r="I1" s="113"/>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
-      <c r="V1" s="113"/>
-      <c r="W1" s="113"/>
+      <c r="H1" s="110"/>
+      <c r="I1" s="110"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
+      <c r="V1" s="110"/>
+      <c r="W1" s="110"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
@@ -5442,32 +5442,32 @@
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A8" s="103" t="s">
+      <c r="A8" s="104" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="104"/>
-      <c r="C8" s="104"/>
-      <c r="D8" s="104"/>
-      <c r="E8" s="104"/>
-      <c r="F8" s="105"/>
+      <c r="B8" s="105"/>
+      <c r="C8" s="105"/>
+      <c r="D8" s="105"/>
+      <c r="E8" s="105"/>
+      <c r="F8" s="106"/>
       <c r="G8" s="4"/>
-      <c r="I8" s="103" t="s">
+      <c r="I8" s="104" t="s">
         <v>10</v>
       </c>
-      <c r="J8" s="104"/>
-      <c r="K8" s="104"/>
-      <c r="L8" s="104"/>
-      <c r="M8" s="104"/>
-      <c r="N8" s="105"/>
+      <c r="J8" s="105"/>
+      <c r="K8" s="105"/>
+      <c r="L8" s="105"/>
+      <c r="M8" s="105"/>
+      <c r="N8" s="106"/>
       <c r="O8" s="1"/>
-      <c r="Q8" s="103" t="s">
+      <c r="Q8" s="104" t="s">
         <v>11</v>
       </c>
-      <c r="R8" s="104"/>
-      <c r="S8" s="104"/>
-      <c r="T8" s="104"/>
-      <c r="U8" s="104"/>
-      <c r="V8" s="105"/>
+      <c r="R8" s="105"/>
+      <c r="S8" s="105"/>
+      <c r="T8" s="105"/>
+      <c r="U8" s="105"/>
+      <c r="V8" s="106"/>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
@@ -5549,11 +5549,11 @@
         <f t="shared" ref="E10:E15" si="0">D10*B10</f>
         <v>0.5</v>
       </c>
-      <c r="F10" s="109">
+      <c r="F10" s="107">
         <f>D10+D11+D12+D13</f>
         <v>2</v>
       </c>
-      <c r="G10" s="74">
+      <c r="G10" s="100">
         <v>1.5</v>
       </c>
       <c r="I10" s="1" t="s">
@@ -5573,11 +5573,11 @@
         <f t="shared" ref="M10:M16" si="2">L10*J10</f>
         <v>0.5</v>
       </c>
-      <c r="N10" s="109">
+      <c r="N10" s="107">
         <f>L10+L11+L12+L13+L14+L15+L16</f>
         <v>3.5</v>
       </c>
-      <c r="O10" s="74">
+      <c r="O10" s="100">
         <v>4</v>
       </c>
       <c r="Q10" s="1" t="s">
@@ -5597,7 +5597,7 @@
         <f>T10*R10</f>
         <v>0.5</v>
       </c>
-      <c r="V10" s="106">
+      <c r="V10" s="111">
         <f>T10+T11+T12</f>
         <v>1.84</v>
       </c>
@@ -5620,8 +5620,8 @@
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="F11" s="112"/>
-      <c r="G11" s="74"/>
+      <c r="F11" s="108"/>
+      <c r="G11" s="100"/>
       <c r="I11" s="1" t="s">
         <v>19</v>
       </c>
@@ -5639,8 +5639,8 @@
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
-      <c r="N11" s="112"/>
-      <c r="O11" s="74"/>
+      <c r="N11" s="108"/>
+      <c r="O11" s="100"/>
       <c r="Q11" s="1" t="s">
         <v>19</v>
       </c>
@@ -5658,7 +5658,7 @@
         <f>T11*R11</f>
         <v>0.5</v>
       </c>
-      <c r="V11" s="107"/>
+      <c r="V11" s="112"/>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
@@ -5678,8 +5678,8 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F12" s="112"/>
-      <c r="G12" s="74"/>
+      <c r="F12" s="108"/>
+      <c r="G12" s="100"/>
       <c r="I12" s="1" t="s">
         <v>20</v>
       </c>
@@ -5697,8 +5697,8 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="N12" s="112"/>
-      <c r="O12" s="74"/>
+      <c r="N12" s="108"/>
+      <c r="O12" s="100"/>
       <c r="Q12" s="1" t="s">
         <v>21</v>
       </c>
@@ -5716,7 +5716,7 @@
         <f>T12*R12</f>
         <v>1.6800000000000002</v>
       </c>
-      <c r="V12" s="108"/>
+      <c r="V12" s="113"/>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
@@ -5736,8 +5736,8 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F13" s="110"/>
-      <c r="G13" s="74"/>
+      <c r="F13" s="109"/>
+      <c r="G13" s="100"/>
       <c r="I13" s="1" t="s">
         <v>23</v>
       </c>
@@ -5755,8 +5755,8 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="N13" s="112"/>
-      <c r="O13" s="74"/>
+      <c r="N13" s="108"/>
+      <c r="O13" s="100"/>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
@@ -5776,11 +5776,11 @@
         <f t="shared" si="0"/>
         <v>1.575</v>
       </c>
-      <c r="F14" s="109">
+      <c r="F14" s="107">
         <f>D10+D11+D12+D14+D15</f>
         <v>3.09375</v>
       </c>
-      <c r="G14" s="74">
+      <c r="G14" s="100">
         <v>3</v>
       </c>
       <c r="I14" s="1" t="s">
@@ -5800,8 +5800,8 @@
         <f t="shared" si="2"/>
         <v>3.5</v>
       </c>
-      <c r="N14" s="112"/>
-      <c r="O14" s="74"/>
+      <c r="N14" s="108"/>
+      <c r="O14" s="100"/>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
@@ -5821,8 +5821,8 @@
         <f t="shared" si="0"/>
         <v>2.4187500000000002</v>
       </c>
-      <c r="F15" s="110"/>
-      <c r="G15" s="74"/>
+      <c r="F15" s="109"/>
+      <c r="G15" s="100"/>
       <c r="I15" s="1" t="s">
         <v>27</v>
       </c>
@@ -5840,8 +5840,8 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="N15" s="112"/>
-      <c r="O15" s="74"/>
+      <c r="N15" s="108"/>
+      <c r="O15" s="100"/>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.15">
       <c r="D16" s="6" t="s">
@@ -5872,8 +5872,8 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="N16" s="110"/>
-      <c r="O16" s="74"/>
+      <c r="N16" s="109"/>
+      <c r="O16" s="100"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D17" s="6" t="s">
@@ -5922,21 +5922,21 @@
       <c r="F19" s="6"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A20" s="103" t="s">
+      <c r="A20" s="104" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="104"/>
-      <c r="C20" s="104"/>
-      <c r="D20" s="104"/>
-      <c r="E20" s="105"/>
-      <c r="I20" s="103" t="s">
+      <c r="B20" s="105"/>
+      <c r="C20" s="105"/>
+      <c r="D20" s="105"/>
+      <c r="E20" s="106"/>
+      <c r="I20" s="104" t="s">
         <v>30</v>
       </c>
-      <c r="J20" s="104"/>
-      <c r="K20" s="104"/>
-      <c r="L20" s="104"/>
-      <c r="M20" s="104"/>
-      <c r="N20" s="105"/>
+      <c r="J20" s="105"/>
+      <c r="K20" s="105"/>
+      <c r="L20" s="105"/>
+      <c r="M20" s="105"/>
+      <c r="N20" s="106"/>
       <c r="O20" s="5"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.15">
@@ -6009,7 +6009,7 @@
         <f t="shared" ref="M22:M26" si="3">L22*J22</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N22" s="106">
+      <c r="N22" s="111">
         <f>L22+L23+L24</f>
         <v>0.84000000000000008</v>
       </c>
@@ -6049,7 +6049,7 @@
         <f t="shared" si="3"/>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N23" s="107"/>
+      <c r="N23" s="112"/>
       <c r="O23" s="5"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.15">
@@ -6086,7 +6086,7 @@
         <f t="shared" si="3"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="N24" s="108"/>
+      <c r="N24" s="113"/>
       <c r="O24" s="5"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.15">
@@ -6123,7 +6123,7 @@
         <f t="shared" si="3"/>
         <v>0.68</v>
       </c>
-      <c r="N25" s="106">
+      <c r="N25" s="111">
         <f>L22+L23+L25+L26</f>
         <v>1.2400000000000002</v>
       </c>
@@ -6146,7 +6146,7 @@
         <f t="shared" si="3"/>
         <v>0.68</v>
       </c>
-      <c r="N26" s="108"/>
+      <c r="N26" s="113"/>
       <c r="O26" s="5"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.15">
@@ -6160,23 +6160,23 @@
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A30" s="111" t="s">
+      <c r="A30" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="B30" s="104"/>
-      <c r="C30" s="104"/>
-      <c r="D30" s="104"/>
-      <c r="E30" s="104"/>
-      <c r="F30" s="105"/>
+      <c r="B30" s="105"/>
+      <c r="C30" s="105"/>
+      <c r="D30" s="105"/>
+      <c r="E30" s="105"/>
+      <c r="F30" s="106"/>
       <c r="G30" s="4"/>
-      <c r="I30" s="111" t="s">
+      <c r="I30" s="114" t="s">
         <v>44</v>
       </c>
-      <c r="J30" s="104"/>
-      <c r="K30" s="104"/>
-      <c r="L30" s="104"/>
-      <c r="M30" s="104"/>
-      <c r="N30" s="105"/>
+      <c r="J30" s="105"/>
+      <c r="K30" s="105"/>
+      <c r="L30" s="105"/>
+      <c r="M30" s="105"/>
+      <c r="N30" s="106"/>
       <c r="O30" s="1"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.15">
@@ -6241,11 +6241,11 @@
         <f t="shared" ref="E32:E37" si="4">D32*B32</f>
         <v>0.70724999999999993</v>
       </c>
-      <c r="F32" s="109">
+      <c r="F32" s="107">
         <f>D32+D33+D34+D35</f>
         <v>2.8634999999999997</v>
       </c>
-      <c r="G32" s="74">
+      <c r="G32" s="100">
         <v>1.5</v>
       </c>
       <c r="I32" s="1" t="s">
@@ -6265,11 +6265,11 @@
         <f t="shared" ref="M32:M38" si="6">L32*J32</f>
         <v>0.70724999999999993</v>
       </c>
-      <c r="N32" s="109">
+      <c r="N32" s="107">
         <f>L32+L33+L34+L35+L36+L37+L38</f>
         <v>4.4731499999999995</v>
       </c>
-      <c r="O32" s="74">
+      <c r="O32" s="100">
         <v>4</v>
       </c>
     </row>
@@ -6291,8 +6291,8 @@
         <f t="shared" si="4"/>
         <v>0.70724999999999993</v>
       </c>
-      <c r="F33" s="112"/>
-      <c r="G33" s="74"/>
+      <c r="F33" s="108"/>
+      <c r="G33" s="100"/>
       <c r="I33" s="1" t="s">
         <v>19</v>
       </c>
@@ -6310,8 +6310,8 @@
         <f t="shared" si="6"/>
         <v>0.70724999999999993</v>
       </c>
-      <c r="N33" s="112"/>
-      <c r="O33" s="74"/>
+      <c r="N33" s="108"/>
+      <c r="O33" s="100"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
@@ -6331,8 +6331,8 @@
         <f t="shared" si="4"/>
         <v>1.4489999999999998</v>
       </c>
-      <c r="F34" s="112"/>
-      <c r="G34" s="74"/>
+      <c r="F34" s="108"/>
+      <c r="G34" s="100"/>
       <c r="I34" s="1" t="s">
         <v>20</v>
       </c>
@@ -6350,8 +6350,8 @@
         <f t="shared" si="6"/>
         <v>1.4489999999999998</v>
       </c>
-      <c r="N34" s="112"/>
-      <c r="O34" s="74"/>
+      <c r="N34" s="108"/>
+      <c r="O34" s="100"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
@@ -6371,8 +6371,8 @@
         <f t="shared" si="4"/>
         <v>1.4489999999999998</v>
       </c>
-      <c r="F35" s="110"/>
-      <c r="G35" s="74"/>
+      <c r="F35" s="109"/>
+      <c r="G35" s="100"/>
       <c r="I35" s="1" t="s">
         <v>23</v>
       </c>
@@ -6390,8 +6390,8 @@
         <f t="shared" si="6"/>
         <v>6.1749999999999989</v>
       </c>
-      <c r="N35" s="112"/>
-      <c r="O35" s="74"/>
+      <c r="N35" s="108"/>
+      <c r="O35" s="100"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
@@ -6411,11 +6411,11 @@
         <f t="shared" si="4"/>
         <v>2.1</v>
       </c>
-      <c r="F36" s="109">
+      <c r="F36" s="107">
         <f>D32+D33+D34+D36+D37</f>
         <v>4.2640000000000002</v>
       </c>
-      <c r="G36" s="74">
+      <c r="G36" s="100">
         <v>3</v>
       </c>
       <c r="I36" s="1" t="s">
@@ -6435,8 +6435,8 @@
         <f t="shared" si="6"/>
         <v>4.0631500000000003</v>
       </c>
-      <c r="N36" s="112"/>
-      <c r="O36" s="74"/>
+      <c r="N36" s="108"/>
+      <c r="O36" s="100"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
@@ -6456,8 +6456,8 @@
         <f t="shared" si="4"/>
         <v>3.2249999999999996</v>
       </c>
-      <c r="F37" s="110"/>
-      <c r="G37" s="74"/>
+      <c r="F37" s="109"/>
+      <c r="G37" s="100"/>
       <c r="I37" s="1" t="s">
         <v>27</v>
       </c>
@@ -6475,8 +6475,8 @@
         <f t="shared" si="6"/>
         <v>6.1749999999999989</v>
       </c>
-      <c r="N37" s="112"/>
-      <c r="O37" s="74"/>
+      <c r="N37" s="108"/>
+      <c r="O37" s="100"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D38" s="6" t="s">
@@ -6507,8 +6507,8 @@
         <f t="shared" si="6"/>
         <v>1.0373999999999999</v>
       </c>
-      <c r="N38" s="110"/>
-      <c r="O38" s="74"/>
+      <c r="N38" s="109"/>
+      <c r="O38" s="100"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D39" s="6" t="s">
@@ -6553,21 +6553,21 @@
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A43" s="103" t="s">
+      <c r="A43" s="104" t="s">
         <v>29</v>
       </c>
-      <c r="B43" s="104"/>
-      <c r="C43" s="104"/>
-      <c r="D43" s="104"/>
-      <c r="E43" s="105"/>
-      <c r="I43" s="103" t="s">
+      <c r="B43" s="105"/>
+      <c r="C43" s="105"/>
+      <c r="D43" s="105"/>
+      <c r="E43" s="106"/>
+      <c r="I43" s="104" t="s">
         <v>30</v>
       </c>
-      <c r="J43" s="104"/>
-      <c r="K43" s="104"/>
-      <c r="L43" s="104"/>
-      <c r="M43" s="104"/>
-      <c r="N43" s="105"/>
+      <c r="J43" s="105"/>
+      <c r="K43" s="105"/>
+      <c r="L43" s="105"/>
+      <c r="M43" s="105"/>
+      <c r="N43" s="106"/>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
@@ -6638,7 +6638,7 @@
         <f t="shared" ref="M45:M49" si="7">L45*J45</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N45" s="106">
+      <c r="N45" s="111">
         <f>L45+L46+L47</f>
         <v>0.84000000000000008</v>
       </c>
@@ -6677,7 +6677,7 @@
         <f t="shared" si="7"/>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N46" s="107"/>
+      <c r="N46" s="112"/>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
@@ -6713,7 +6713,7 @@
         <f t="shared" si="7"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="N47" s="108"/>
+      <c r="N47" s="113"/>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
@@ -6749,7 +6749,7 @@
         <f t="shared" si="7"/>
         <v>0.68</v>
       </c>
-      <c r="N48" s="106">
+      <c r="N48" s="111">
         <f>L45+L46+L48+L49</f>
         <v>1.2400000000000002</v>
       </c>
@@ -6771,10 +6771,29 @@
         <f t="shared" si="7"/>
         <v>0.68</v>
       </c>
-      <c r="N49" s="108"/>
+      <c r="N49" s="113"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="I43:N43"/>
+    <mergeCell ref="N45:N47"/>
+    <mergeCell ref="N48:N49"/>
+    <mergeCell ref="O32:O38"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="I30:N30"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="G32:G35"/>
+    <mergeCell ref="N32:N38"/>
+    <mergeCell ref="N22:N24"/>
+    <mergeCell ref="N25:N26"/>
+    <mergeCell ref="V10:V12"/>
+    <mergeCell ref="G10:G13"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="O10:O16"/>
+    <mergeCell ref="N10:N16"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="I20:N20"/>
     <mergeCell ref="F10:F13"/>
@@ -6784,25 +6803,6 @@
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="I8:N8"/>
     <mergeCell ref="Q8:V8"/>
-    <mergeCell ref="N22:N24"/>
-    <mergeCell ref="N25:N26"/>
-    <mergeCell ref="V10:V12"/>
-    <mergeCell ref="G10:G13"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="O10:O16"/>
-    <mergeCell ref="N10:N16"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="I30:N30"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="G32:G35"/>
-    <mergeCell ref="N32:N38"/>
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="I43:N43"/>
-    <mergeCell ref="N45:N47"/>
-    <mergeCell ref="N48:N49"/>
-    <mergeCell ref="O32:O38"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
